--- a/research/traditional_assets/database/data/qatar/qatar_entertainment.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_entertainment.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.4320000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="E2">
-        <v>-0.245</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G2">
-        <v>-9.567307692307693</v>
+        <v>-2.070175438596491</v>
       </c>
       <c r="H2">
-        <v>-9.567307692307693</v>
+        <v>-2.070175438596491</v>
       </c>
       <c r="I2">
-        <v>-15.09615384615385</v>
+        <v>-2.947368421052632</v>
       </c>
       <c r="J2">
-        <v>-15.09615384615385</v>
+        <v>-2.947368421052632</v>
       </c>
       <c r="K2">
-        <v>1.02</v>
+        <v>0.706</v>
       </c>
       <c r="L2">
-        <v>4.903846153846154</v>
+        <v>0.6192982456140351</v>
       </c>
       <c r="M2">
-        <v>1.69</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>0.02761437908496732</v>
+        <v>0.02011173184357542</v>
       </c>
       <c r="O2">
-        <v>1.656862745098039</v>
+        <v>1.529745042492918</v>
       </c>
       <c r="P2">
-        <v>1.69</v>
+        <v>1.08</v>
       </c>
       <c r="Q2">
-        <v>0.02761437908496732</v>
+        <v>0.02011173184357542</v>
       </c>
       <c r="R2">
-        <v>1.656862745098039</v>
+        <v>1.529745042492918</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="V2">
-        <v>0.06633986928104574</v>
+        <v>0.07672253258845438</v>
       </c>
       <c r="W2">
-        <v>0.02779291553133515</v>
+        <v>0.01853018372703412</v>
       </c>
       <c r="X2">
-        <v>0.06868666426055199</v>
+        <v>0.1189187068446385</v>
       </c>
       <c r="Y2">
-        <v>-0.04089374872921685</v>
+        <v>-0.1003885231176044</v>
       </c>
       <c r="Z2">
-        <v>0.005836139169472503</v>
+        <v>0.03074433656957928</v>
       </c>
       <c r="AA2">
-        <v>-0.08810325476992144</v>
+        <v>-0.09061488673139156</v>
       </c>
       <c r="AB2">
-        <v>0.06632030582549372</v>
+        <v>0.1161857047055994</v>
       </c>
       <c r="AC2">
-        <v>-0.1544235605954152</v>
+        <v>-0.2068005914369909</v>
       </c>
       <c r="AD2">
-        <v>3.56</v>
+        <v>2.59</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.56</v>
+        <v>2.59</v>
       </c>
       <c r="AG2">
-        <v>-0.4999999999999996</v>
+        <v>-1.53</v>
       </c>
       <c r="AH2">
-        <v>0.05497220506485485</v>
+        <v>0.04601172499555871</v>
       </c>
       <c r="AI2">
-        <v>0.08712677435144396</v>
+        <v>0.06412478336221837</v>
       </c>
       <c r="AJ2">
-        <v>-0.008237232289950569</v>
+        <v>-0.0293271995399655</v>
       </c>
       <c r="AK2">
-        <v>-0.01358695652173912</v>
+        <v>-0.04218362282878413</v>
       </c>
       <c r="AL2">
-        <v>0.232</v>
+        <v>0.146</v>
       </c>
       <c r="AM2">
-        <v>-0.01199999999999998</v>
+        <v>-0.198</v>
       </c>
       <c r="AN2">
-        <v>-1.736585365853659</v>
+        <v>-1.135964912280702</v>
       </c>
       <c r="AO2">
-        <v>-13.53448275862069</v>
+        <v>-23.01369863013699</v>
       </c>
       <c r="AP2">
-        <v>0.24390243902439</v>
+        <v>0.6710526315789476</v>
       </c>
       <c r="AQ2">
-        <v>261.666666666667</v>
+        <v>16.96969696969697</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qatar Cinema and Film Distribution Company - Q.S.C (DSM:QCFS)</t>
+          <t>Qatar Cinema and Film Distribution Co. (Q.P.S.C) (DSM:QCFS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.4320000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="E3">
-        <v>-0.245</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G3">
-        <v>-9.567307692307693</v>
+        <v>-2.070175438596491</v>
       </c>
       <c r="H3">
-        <v>-9.567307692307693</v>
+        <v>-2.070175438596491</v>
       </c>
       <c r="I3">
-        <v>-15.09615384615385</v>
+        <v>-2.947368421052632</v>
       </c>
       <c r="J3">
-        <v>-15.09615384615385</v>
+        <v>-2.947368421052632</v>
       </c>
       <c r="K3">
-        <v>1.02</v>
+        <v>0.706</v>
       </c>
       <c r="L3">
-        <v>4.903846153846154</v>
+        <v>0.6192982456140351</v>
       </c>
       <c r="M3">
-        <v>1.69</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>0.02761437908496732</v>
+        <v>0.02011173184357542</v>
       </c>
       <c r="O3">
-        <v>1.656862745098039</v>
+        <v>1.529745042492918</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.08</v>
       </c>
       <c r="Q3">
-        <v>0.02761437908496732</v>
+        <v>0.02011173184357542</v>
       </c>
       <c r="R3">
-        <v>1.656862745098039</v>
+        <v>1.529745042492918</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="V3">
-        <v>0.06633986928104574</v>
+        <v>0.07672253258845438</v>
       </c>
       <c r="W3">
-        <v>0.02779291553133515</v>
+        <v>0.01853018372703412</v>
       </c>
       <c r="X3">
-        <v>0.06868666426055199</v>
+        <v>0.1189187068446385</v>
       </c>
       <c r="Y3">
-        <v>-0.04089374872921685</v>
+        <v>-0.1003885231176044</v>
       </c>
       <c r="Z3">
-        <v>0.005836139169472503</v>
+        <v>0.03074433656957928</v>
       </c>
       <c r="AA3">
-        <v>-0.08810325476992144</v>
+        <v>-0.09061488673139156</v>
       </c>
       <c r="AB3">
-        <v>0.06632030582549372</v>
+        <v>0.1161857047055994</v>
       </c>
       <c r="AC3">
-        <v>-0.1544235605954152</v>
+        <v>-0.2068005914369909</v>
       </c>
       <c r="AD3">
-        <v>3.56</v>
+        <v>2.59</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.56</v>
+        <v>2.59</v>
       </c>
       <c r="AG3">
-        <v>-0.4999999999999996</v>
+        <v>-1.53</v>
       </c>
       <c r="AH3">
-        <v>0.05497220506485485</v>
+        <v>0.04601172499555871</v>
       </c>
       <c r="AI3">
-        <v>0.08712677435144396</v>
+        <v>0.06412478336221837</v>
       </c>
       <c r="AJ3">
-        <v>-0.008237232289950569</v>
+        <v>-0.0293271995399655</v>
       </c>
       <c r="AK3">
-        <v>-0.01358695652173912</v>
+        <v>-0.04218362282878413</v>
       </c>
       <c r="AL3">
-        <v>0.232</v>
+        <v>0.146</v>
       </c>
       <c r="AM3">
-        <v>-0.01199999999999998</v>
+        <v>-0.198</v>
       </c>
       <c r="AN3">
-        <v>-1.736585365853659</v>
+        <v>-1.135964912280702</v>
       </c>
       <c r="AO3">
-        <v>-13.53448275862069</v>
+        <v>-23.01369863013699</v>
       </c>
       <c r="AP3">
-        <v>0.24390243902439</v>
+        <v>0.6710526315789476</v>
       </c>
       <c r="AQ3">
-        <v>261.666666666667</v>
+        <v>16.96969696969697</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_entertainment.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_entertainment.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.14</v>
+        <v>-0.0358</v>
       </c>
       <c r="E2">
-        <v>-0.09300000000000001</v>
+        <v>-0.0747</v>
       </c>
       <c r="G2">
-        <v>-2.070175438596491</v>
+        <v>-1.320754716981132</v>
       </c>
       <c r="H2">
-        <v>-2.070175438596491</v>
+        <v>-1.320754716981132</v>
       </c>
       <c r="I2">
-        <v>-2.947368421052632</v>
+        <v>-1.779874213836478</v>
       </c>
       <c r="J2">
-        <v>-2.947368421052632</v>
+        <v>-1.779874213836478</v>
       </c>
       <c r="K2">
-        <v>0.706</v>
+        <v>1.24</v>
       </c>
       <c r="L2">
-        <v>0.6192982456140351</v>
+        <v>0.7798742138364779</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>0.02011173184357542</v>
+        <v>0.0208</v>
       </c>
       <c r="O2">
-        <v>1.529745042492918</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="P2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Q2">
-        <v>0.02011173184357542</v>
+        <v>0.0208</v>
       </c>
       <c r="R2">
-        <v>1.529745042492918</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.12</v>
+        <v>5.75</v>
       </c>
       <c r="V2">
-        <v>0.07672253258845438</v>
+        <v>0.115</v>
       </c>
       <c r="W2">
-        <v>0.01853018372703412</v>
+        <v>0.03280423280423281</v>
       </c>
       <c r="X2">
-        <v>0.1189187068446385</v>
+        <v>0.09722382115924913</v>
       </c>
       <c r="Y2">
-        <v>-0.1003885231176044</v>
+        <v>-0.06441958835501632</v>
       </c>
       <c r="Z2">
-        <v>0.03074433656957928</v>
+        <v>0.04383788254755996</v>
       </c>
       <c r="AA2">
-        <v>-0.09061488673139156</v>
+        <v>-0.07802591673559416</v>
       </c>
       <c r="AB2">
-        <v>0.1161857047055994</v>
+        <v>0.09462991013088727</v>
       </c>
       <c r="AC2">
-        <v>-0.2068005914369909</v>
+        <v>-0.1726558268664814</v>
       </c>
       <c r="AD2">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AG2">
-        <v>-1.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AH2">
-        <v>0.04601172499555871</v>
+        <v>0.05105333080280888</v>
       </c>
       <c r="AI2">
-        <v>0.06412478336221837</v>
+        <v>0.07007033081531648</v>
       </c>
       <c r="AJ2">
-        <v>-0.0293271995399655</v>
+        <v>-0.0651896037494674</v>
       </c>
       <c r="AK2">
-        <v>-0.04218362282878413</v>
+        <v>-0.09375</v>
       </c>
       <c r="AL2">
-        <v>0.146</v>
+        <v>0.125</v>
       </c>
       <c r="AM2">
-        <v>-0.198</v>
+        <v>-0.263</v>
       </c>
       <c r="AN2">
-        <v>-1.135964912280702</v>
+        <v>-1.68125</v>
       </c>
       <c r="AO2">
-        <v>-23.01369863013699</v>
+        <v>-22.64</v>
       </c>
       <c r="AP2">
-        <v>0.6710526315789476</v>
+        <v>1.9125</v>
       </c>
       <c r="AQ2">
-        <v>16.96969696969697</v>
+        <v>10.76045627376426</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.14</v>
+        <v>-0.0358</v>
       </c>
       <c r="E3">
-        <v>-0.09300000000000001</v>
+        <v>-0.0747</v>
       </c>
       <c r="G3">
-        <v>-2.070175438596491</v>
+        <v>-1.320754716981132</v>
       </c>
       <c r="H3">
-        <v>-2.070175438596491</v>
+        <v>-1.320754716981132</v>
       </c>
       <c r="I3">
-        <v>-2.947368421052632</v>
+        <v>-1.779874213836478</v>
       </c>
       <c r="J3">
-        <v>-2.947368421052632</v>
+        <v>-1.779874213836478</v>
       </c>
       <c r="K3">
-        <v>0.706</v>
+        <v>1.24</v>
       </c>
       <c r="L3">
-        <v>0.6192982456140351</v>
+        <v>0.7798742138364779</v>
       </c>
       <c r="M3">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>0.02011173184357542</v>
+        <v>0.0208</v>
       </c>
       <c r="O3">
-        <v>1.529745042492918</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="P3">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Q3">
-        <v>0.02011173184357542</v>
+        <v>0.0208</v>
       </c>
       <c r="R3">
-        <v>1.529745042492918</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.12</v>
+        <v>5.75</v>
       </c>
       <c r="V3">
-        <v>0.07672253258845438</v>
+        <v>0.115</v>
       </c>
       <c r="W3">
-        <v>0.01853018372703412</v>
+        <v>0.03280423280423281</v>
       </c>
       <c r="X3">
-        <v>0.1189187068446385</v>
+        <v>0.09722382115924913</v>
       </c>
       <c r="Y3">
-        <v>-0.1003885231176044</v>
+        <v>-0.06441958835501632</v>
       </c>
       <c r="Z3">
-        <v>0.03074433656957928</v>
+        <v>0.04383788254755996</v>
       </c>
       <c r="AA3">
-        <v>-0.09061488673139156</v>
+        <v>-0.07802591673559416</v>
       </c>
       <c r="AB3">
-        <v>0.1161857047055994</v>
+        <v>0.09462991013088727</v>
       </c>
       <c r="AC3">
-        <v>-0.2068005914369909</v>
+        <v>-0.1726558268664814</v>
       </c>
       <c r="AD3">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AG3">
-        <v>-1.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AH3">
-        <v>0.04601172499555871</v>
+        <v>0.05105333080280888</v>
       </c>
       <c r="AI3">
-        <v>0.06412478336221837</v>
+        <v>0.07007033081531648</v>
       </c>
       <c r="AJ3">
-        <v>-0.0293271995399655</v>
+        <v>-0.0651896037494674</v>
       </c>
       <c r="AK3">
-        <v>-0.04218362282878413</v>
+        <v>-0.09375</v>
       </c>
       <c r="AL3">
-        <v>0.146</v>
+        <v>0.125</v>
       </c>
       <c r="AM3">
-        <v>-0.198</v>
+        <v>-0.263</v>
       </c>
       <c r="AN3">
-        <v>-1.135964912280702</v>
+        <v>-1.68125</v>
       </c>
       <c r="AO3">
-        <v>-23.01369863013699</v>
+        <v>-22.64</v>
       </c>
       <c r="AP3">
-        <v>0.6710526315789476</v>
+        <v>1.9125</v>
       </c>
       <c r="AQ3">
-        <v>16.96969696969697</v>
+        <v>10.76045627376426</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_entertainment.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_entertainment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.096564792400074</v>
+        <v>0.09650872760767393</v>
       </c>
       <c r="C2">
-        <v>44.19661883432261</v>
+        <v>43.79570058219839</v>
       </c>
       <c r="D2">
-        <v>37.06661883432261</v>
+        <v>37.10760058219839</v>
       </c>
       <c r="E2">
-        <v>-2.79</v>
+        <v>-2.3481</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4419</v>
       </c>
       <c r="G2">
         <v>7.13</v>
@@ -1451,28 +1451,28 @@
         <v>2.068</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02222757</v>
       </c>
       <c r="N2">
-        <v>2.068</v>
+        <v>2.04577243</v>
       </c>
       <c r="O2">
-        <v>0.2068</v>
+        <v>0.204577243</v>
       </c>
       <c r="P2">
-        <v>1.8612</v>
+        <v>1.841195187</v>
       </c>
       <c r="Q2">
-        <v>1.8632</v>
+        <v>1.843195187</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.096564792400074</v>
+        <v>0.09702629051280194</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.026762348933536</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>93.03761049903341</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09650872760767393</v>
+        <v>0.09645266281527384</v>
       </c>
       <c r="C3">
-        <v>43.79570058219839</v>
+        <v>43.3948730511956</v>
       </c>
       <c r="D3">
-        <v>37.10760058219839</v>
+        <v>37.14867305119559</v>
       </c>
       <c r="E3">
-        <v>-2.3481</v>
+        <v>-1.9062</v>
       </c>
       <c r="F3">
-        <v>0.4419</v>
+        <v>0.8837999999999999</v>
       </c>
       <c r="G3">
         <v>7.13</v>
@@ -1533,28 +1533,28 @@
         <v>2.068</v>
       </c>
       <c r="M3">
-        <v>0.02222757</v>
+        <v>0.04445514</v>
       </c>
       <c r="N3">
-        <v>2.04577243</v>
+        <v>2.02354486</v>
       </c>
       <c r="O3">
-        <v>0.204577243</v>
+        <v>0.202354486</v>
       </c>
       <c r="P3">
-        <v>1.841195187</v>
+        <v>1.821190374</v>
       </c>
       <c r="Q3">
-        <v>1.843195187</v>
+        <v>1.823190374</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09702629051280194</v>
+        <v>0.09749720695436107</v>
       </c>
       <c r="T3">
-        <v>1.026762348933536</v>
+        <v>1.036201237965836</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>93.03761049903341</v>
+        <v>46.5188052495167</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09645266281527384</v>
+        <v>0.09639659802287377</v>
       </c>
       <c r="C4">
-        <v>43.3948730511956</v>
+        <v>42.99413654289146</v>
       </c>
       <c r="D4">
-        <v>37.14867305119559</v>
+        <v>37.18983654289146</v>
       </c>
       <c r="E4">
-        <v>-1.9062</v>
+        <v>-1.4643</v>
       </c>
       <c r="F4">
-        <v>0.8837999999999999</v>
+        <v>1.3257</v>
       </c>
       <c r="G4">
         <v>7.13</v>
@@ -1615,28 +1615,28 @@
         <v>2.068</v>
       </c>
       <c r="M4">
-        <v>0.04445514</v>
+        <v>0.06668270999999999</v>
       </c>
       <c r="N4">
-        <v>2.02354486</v>
+        <v>2.00131729</v>
       </c>
       <c r="O4">
-        <v>0.202354486</v>
+        <v>0.200131729</v>
       </c>
       <c r="P4">
-        <v>1.821190374</v>
+        <v>1.801185561</v>
       </c>
       <c r="Q4">
-        <v>1.823190374</v>
+        <v>1.803185561</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09749720695436107</v>
+        <v>0.09797783301327193</v>
       </c>
       <c r="T4">
-        <v>1.036201237965836</v>
+        <v>1.045834743266842</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>46.5188052495167</v>
+        <v>31.01253683301114</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09639659802287377</v>
+        <v>0.09634053323047372</v>
       </c>
       <c r="C5">
-        <v>42.99413654289146</v>
+        <v>42.59349136020137</v>
       </c>
       <c r="D5">
-        <v>37.18983654289146</v>
+        <v>37.23109136020137</v>
       </c>
       <c r="E5">
-        <v>-1.4643</v>
+        <v>-1.0224</v>
       </c>
       <c r="F5">
-        <v>1.3257</v>
+        <v>1.7676</v>
       </c>
       <c r="G5">
         <v>7.13</v>
@@ -1697,28 +1697,28 @@
         <v>2.068</v>
       </c>
       <c r="M5">
-        <v>0.06668270999999999</v>
+        <v>0.08891027999999999</v>
       </c>
       <c r="N5">
-        <v>2.00131729</v>
+        <v>1.97908972</v>
       </c>
       <c r="O5">
-        <v>0.200131729</v>
+        <v>0.197908972</v>
       </c>
       <c r="P5">
-        <v>1.801185561</v>
+        <v>1.781180748</v>
       </c>
       <c r="Q5">
-        <v>1.803185561</v>
+        <v>1.783180748</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09797783301327193</v>
+        <v>0.09846847211507678</v>
       </c>
       <c r="T5">
-        <v>1.045834743266842</v>
+        <v>1.055668946594953</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.01253683301114</v>
+        <v>23.25940262475835</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09634053323047372</v>
+        <v>0.09628446843807362</v>
       </c>
       <c r="C6">
-        <v>42.59349136020137</v>
+        <v>42.1929378073864</v>
       </c>
       <c r="D6">
-        <v>37.23109136020137</v>
+        <v>37.2724378073864</v>
       </c>
       <c r="E6">
-        <v>-1.0224</v>
+        <v>-0.5805000000000002</v>
       </c>
       <c r="F6">
-        <v>1.7676</v>
+        <v>2.2095</v>
       </c>
       <c r="G6">
         <v>7.13</v>
@@ -1779,28 +1779,28 @@
         <v>2.068</v>
       </c>
       <c r="M6">
-        <v>0.08891027999999999</v>
+        <v>0.11113785</v>
       </c>
       <c r="N6">
-        <v>1.97908972</v>
+        <v>1.95686215</v>
       </c>
       <c r="O6">
-        <v>0.197908972</v>
+        <v>0.195686215</v>
       </c>
       <c r="P6">
-        <v>1.781180748</v>
+        <v>1.761175935</v>
       </c>
       <c r="Q6">
-        <v>1.783180748</v>
+        <v>1.763175935</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09846847211507678</v>
+        <v>0.09896944046113013</v>
       </c>
       <c r="T6">
-        <v>1.055668946594953</v>
+        <v>1.065710185782603</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.25940262475835</v>
+        <v>18.60752209980668</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09628446843807362</v>
+        <v>0.09622840364567355</v>
       </c>
       <c r="C7">
-        <v>42.1929378073864</v>
+        <v>41.79247619006054</v>
       </c>
       <c r="D7">
-        <v>37.2724378073864</v>
+        <v>37.31387619006054</v>
       </c>
       <c r="E7">
-        <v>-0.5805000000000002</v>
+        <v>-0.1385999999999998</v>
       </c>
       <c r="F7">
-        <v>2.2095</v>
+        <v>2.6514</v>
       </c>
       <c r="G7">
         <v>7.13</v>
@@ -1861,28 +1861,28 @@
         <v>2.068</v>
       </c>
       <c r="M7">
-        <v>0.11113785</v>
+        <v>0.13336542</v>
       </c>
       <c r="N7">
-        <v>1.95686215</v>
+        <v>1.93463458</v>
       </c>
       <c r="O7">
-        <v>0.195686215</v>
+        <v>0.193463458</v>
       </c>
       <c r="P7">
-        <v>1.761175935</v>
+        <v>1.741171122</v>
       </c>
       <c r="Q7">
-        <v>1.763175935</v>
+        <v>1.743171122</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09896944046113013</v>
+        <v>0.09948106770816335</v>
       </c>
       <c r="T7">
-        <v>1.065710185782603</v>
+        <v>1.075965068357225</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.60752209980668</v>
+        <v>15.50626841650557</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09622840364567355</v>
+        <v>0.09617233885327348</v>
       </c>
       <c r="C8">
-        <v>41.79247619006054</v>
+        <v>41.3921068151985</v>
       </c>
       <c r="D8">
-        <v>37.31387619006054</v>
+        <v>37.3554068151985</v>
       </c>
       <c r="E8">
-        <v>-0.1386000000000003</v>
+        <v>0.3032999999999997</v>
       </c>
       <c r="F8">
-        <v>2.6514</v>
+        <v>3.0933</v>
       </c>
       <c r="G8">
         <v>7.13</v>
@@ -1943,28 +1943,28 @@
         <v>2.068</v>
       </c>
       <c r="M8">
-        <v>0.13336542</v>
+        <v>0.15559299</v>
       </c>
       <c r="N8">
-        <v>1.93463458</v>
+        <v>1.91240701</v>
       </c>
       <c r="O8">
-        <v>0.193463458</v>
+        <v>0.191240701</v>
       </c>
       <c r="P8">
-        <v>1.741171122</v>
+        <v>1.721166309</v>
       </c>
       <c r="Q8">
-        <v>1.743171122</v>
+        <v>1.723166309</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09948106770816335</v>
+        <v>0.1000036976916919</v>
       </c>
       <c r="T8">
-        <v>1.075965068357225</v>
+        <v>1.086440486040978</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.50626841650557</v>
+        <v>13.29108721414763</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09617233885327349</v>
+        <v>0.0962242740608734</v>
       </c>
       <c r="C9">
-        <v>41.3921068151985</v>
+        <v>40.91173207571917</v>
       </c>
       <c r="D9">
-        <v>37.35540681519849</v>
+        <v>37.31693207571917</v>
       </c>
       <c r="E9">
-        <v>0.3033000000000001</v>
+        <v>0.7451999999999996</v>
       </c>
       <c r="F9">
-        <v>3.0933</v>
+        <v>3.5352</v>
       </c>
       <c r="G9">
         <v>7.13</v>
@@ -2025,45 +2025,45 @@
         <v>2.068</v>
       </c>
       <c r="M9">
-        <v>0.15559299</v>
+        <v>0.18312336</v>
       </c>
       <c r="N9">
-        <v>1.91240701</v>
+        <v>1.88487664</v>
       </c>
       <c r="O9">
-        <v>0.191240701</v>
+        <v>0.188487664</v>
       </c>
       <c r="P9">
-        <v>1.721166309</v>
+        <v>1.696388976</v>
       </c>
       <c r="Q9">
-        <v>1.723166309</v>
+        <v>1.698388976</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1000036976916919</v>
+        <v>0.1005376891966015</v>
       </c>
       <c r="T9">
-        <v>1.086440486040978</v>
+        <v>1.097143630196117</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.1</v>
       </c>
       <c r="W9">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.29108721414763</v>
+        <v>11.29293389985854</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0962242740608734</v>
+        <v>0.09618170926847334</v>
       </c>
       <c r="C10">
-        <v>40.91173207571917</v>
+        <v>40.50135914159035</v>
       </c>
       <c r="D10">
-        <v>37.31693207571917</v>
+        <v>37.34845914159035</v>
       </c>
       <c r="E10">
-        <v>0.7451999999999996</v>
+        <v>1.1871</v>
       </c>
       <c r="F10">
-        <v>3.5352</v>
+        <v>3.9771</v>
       </c>
       <c r="G10">
         <v>7.13</v>
@@ -2107,28 +2107,28 @@
         <v>2.068</v>
       </c>
       <c r="M10">
-        <v>0.18312336</v>
+        <v>0.20601378</v>
       </c>
       <c r="N10">
-        <v>1.88487664</v>
+        <v>1.86198622</v>
       </c>
       <c r="O10">
-        <v>0.188487664</v>
+        <v>0.186198622</v>
       </c>
       <c r="P10">
-        <v>1.696388976</v>
+        <v>1.675787598</v>
       </c>
       <c r="Q10">
-        <v>1.698388976</v>
+        <v>1.677787598</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1005376891966015</v>
+        <v>0.1010834167785421</v>
       </c>
       <c r="T10">
-        <v>1.097143630196117</v>
+        <v>1.108082008288731</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.29293389985854</v>
+        <v>10.03816346654093</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09618170926847334</v>
+        <v>0.09629214447607327</v>
       </c>
       <c r="C11">
-        <v>40.50135914159035</v>
+        <v>39.97777148736934</v>
       </c>
       <c r="D11">
-        <v>37.34845914159035</v>
+        <v>37.26677148736933</v>
       </c>
       <c r="E11">
-        <v>1.1871</v>
+        <v>1.629</v>
       </c>
       <c r="F11">
-        <v>3.9771</v>
+        <v>4.419</v>
       </c>
       <c r="G11">
         <v>7.13</v>
@@ -2189,45 +2189,45 @@
         <v>2.068</v>
       </c>
       <c r="M11">
-        <v>0.20601378</v>
+        <v>0.2364165</v>
       </c>
       <c r="N11">
-        <v>1.86198622</v>
+        <v>1.8315835</v>
       </c>
       <c r="O11">
-        <v>0.186198622</v>
+        <v>0.18315835</v>
       </c>
       <c r="P11">
-        <v>1.675787598</v>
+        <v>1.64842515</v>
       </c>
       <c r="Q11">
-        <v>1.677787598</v>
+        <v>1.65042515</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1010834167785421</v>
+        <v>0.1016412716400814</v>
       </c>
       <c r="T11">
-        <v>1.108082008288731</v>
+        <v>1.119263461450071</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.1</v>
       </c>
       <c r="W11">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.03816346654093</v>
+        <v>8.747274407666133</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09629214447607327</v>
+        <v>0.09626487968367317</v>
       </c>
       <c r="C12">
-        <v>39.97777148736934</v>
+        <v>39.55600570337052</v>
       </c>
       <c r="D12">
-        <v>37.26677148736933</v>
+        <v>37.28690570337052</v>
       </c>
       <c r="E12">
-        <v>1.629</v>
+        <v>2.0709</v>
       </c>
       <c r="F12">
-        <v>4.419</v>
+        <v>4.8609</v>
       </c>
       <c r="G12">
         <v>7.13</v>
@@ -2271,28 +2271,28 @@
         <v>2.068</v>
       </c>
       <c r="M12">
-        <v>0.2364165</v>
+        <v>0.26005815</v>
       </c>
       <c r="N12">
-        <v>1.8315835</v>
+        <v>1.80794185</v>
       </c>
       <c r="O12">
-        <v>0.18315835</v>
+        <v>0.180794185</v>
       </c>
       <c r="P12">
-        <v>1.64842515</v>
+        <v>1.627147665</v>
       </c>
       <c r="Q12">
-        <v>1.65042515</v>
+        <v>1.629147665</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1016412716400814</v>
+        <v>0.1022116625659249</v>
       </c>
       <c r="T12">
-        <v>1.119263461450071</v>
+        <v>1.130696183221777</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.747274407666133</v>
+        <v>7.952067643332848</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09626487968367317</v>
+        <v>0.09632401489127312</v>
       </c>
       <c r="C13">
-        <v>39.55600570337052</v>
+        <v>39.07046370630687</v>
       </c>
       <c r="D13">
-        <v>37.28690570337052</v>
+        <v>37.24326370630687</v>
       </c>
       <c r="E13">
-        <v>2.0709</v>
+        <v>2.512799999999999</v>
       </c>
       <c r="F13">
-        <v>4.8609</v>
+        <v>5.3028</v>
       </c>
       <c r="G13">
         <v>7.13</v>
@@ -2353,45 +2353,45 @@
         <v>2.068</v>
       </c>
       <c r="M13">
-        <v>0.26005815</v>
+        <v>0.28794204</v>
       </c>
       <c r="N13">
-        <v>1.80794185</v>
+        <v>1.78005796</v>
       </c>
       <c r="O13">
-        <v>0.180794185</v>
+        <v>0.178005796</v>
       </c>
       <c r="P13">
-        <v>1.627147665</v>
+        <v>1.602052164</v>
       </c>
       <c r="Q13">
-        <v>1.629147665</v>
+        <v>1.604052164</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1022116625659249</v>
+        <v>0.1027950169219013</v>
       </c>
       <c r="T13">
-        <v>1.130696183221777</v>
+        <v>1.142388739579205</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.1</v>
       </c>
       <c r="W13">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.952067643332848</v>
+        <v>7.182000933243373</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09632401489127312</v>
+        <v>0.09630395009887303</v>
       </c>
       <c r="C14">
-        <v>39.07046370630687</v>
+        <v>38.64336014011266</v>
       </c>
       <c r="D14">
-        <v>37.24326370630687</v>
+        <v>37.25806014011266</v>
       </c>
       <c r="E14">
-        <v>2.512799999999999</v>
+        <v>2.9547</v>
       </c>
       <c r="F14">
-        <v>5.3028</v>
+        <v>5.7447</v>
       </c>
       <c r="G14">
         <v>7.13</v>
@@ -2435,28 +2435,28 @@
         <v>2.068</v>
       </c>
       <c r="M14">
-        <v>0.28794204</v>
+        <v>0.31193721</v>
       </c>
       <c r="N14">
-        <v>1.78005796</v>
+        <v>1.75606279</v>
       </c>
       <c r="O14">
-        <v>0.178005796</v>
+        <v>0.175606279</v>
       </c>
       <c r="P14">
-        <v>1.602052164</v>
+        <v>1.580456511</v>
       </c>
       <c r="Q14">
-        <v>1.604052164</v>
+        <v>1.582456511</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1027950169219013</v>
+        <v>0.1033917817228426</v>
       </c>
       <c r="T14">
-        <v>1.142388739579205</v>
+        <v>1.154350090335653</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.182000933243373</v>
+        <v>6.629539322993881</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09630395009887303</v>
+        <v>0.09628388530647294</v>
       </c>
       <c r="C15">
-        <v>38.64336014011266</v>
+        <v>38.21626833558738</v>
       </c>
       <c r="D15">
-        <v>37.25806014011266</v>
+        <v>37.27286833558738</v>
       </c>
       <c r="E15">
-        <v>2.9547</v>
+        <v>3.3966</v>
       </c>
       <c r="F15">
-        <v>5.7447</v>
+        <v>6.1866</v>
       </c>
       <c r="G15">
         <v>7.13</v>
@@ -2517,28 +2517,28 @@
         <v>2.068</v>
       </c>
       <c r="M15">
-        <v>0.31193721</v>
+        <v>0.33593238</v>
       </c>
       <c r="N15">
-        <v>1.75606279</v>
+        <v>1.73206762</v>
       </c>
       <c r="O15">
-        <v>0.175606279</v>
+        <v>0.173206762</v>
       </c>
       <c r="P15">
-        <v>1.580456511</v>
+        <v>1.558860858</v>
       </c>
       <c r="Q15">
-        <v>1.582456511</v>
+        <v>1.560860858</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1033917817228426</v>
+        <v>0.1040024247749685</v>
       </c>
       <c r="T15">
-        <v>1.154350090335653</v>
+        <v>1.166589612039926</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.629539322993881</v>
+        <v>6.156000799922889</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09628388530647294</v>
+        <v>0.09639882051407289</v>
       </c>
       <c r="C16">
-        <v>38.21626833558738</v>
+        <v>37.68970302488503</v>
       </c>
       <c r="D16">
-        <v>37.27286833558738</v>
+        <v>37.18820302488503</v>
       </c>
       <c r="E16">
-        <v>3.3966</v>
+        <v>3.838500000000001</v>
       </c>
       <c r="F16">
-        <v>6.1866</v>
+        <v>6.628500000000001</v>
       </c>
       <c r="G16">
         <v>7.13</v>
@@ -2599,45 +2599,45 @@
         <v>2.068</v>
       </c>
       <c r="M16">
-        <v>0.33593238</v>
+        <v>0.3665560500000001</v>
       </c>
       <c r="N16">
-        <v>1.73206762</v>
+        <v>1.70144395</v>
       </c>
       <c r="O16">
-        <v>0.173206762</v>
+        <v>0.170144395</v>
       </c>
       <c r="P16">
-        <v>1.558860858</v>
+        <v>1.531299555</v>
       </c>
       <c r="Q16">
-        <v>1.560860858</v>
+        <v>1.533299555</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1040024247749685</v>
+        <v>0.1046274358989093</v>
       </c>
       <c r="T16">
-        <v>1.166589612039926</v>
+        <v>1.179117122490182</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.156000799922889</v>
+        <v>5.641701998916672</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09639882051407289</v>
+        <v>0.09638775572167282</v>
       </c>
       <c r="C17">
-        <v>37.68970302488503</v>
+        <v>37.25593700395432</v>
       </c>
       <c r="D17">
-        <v>37.18820302488503</v>
+        <v>37.19633700395431</v>
       </c>
       <c r="E17">
-        <v>3.8385</v>
+        <v>4.280399999999999</v>
       </c>
       <c r="F17">
-        <v>6.6285</v>
+        <v>7.070399999999999</v>
       </c>
       <c r="G17">
         <v>7.13</v>
@@ -2681,28 +2681,28 @@
         <v>2.068</v>
       </c>
       <c r="M17">
-        <v>0.36655605</v>
+        <v>0.39099312</v>
       </c>
       <c r="N17">
-        <v>1.70144395</v>
+        <v>1.67700688</v>
       </c>
       <c r="O17">
-        <v>0.170144395</v>
+        <v>0.167700688</v>
       </c>
       <c r="P17">
-        <v>1.531299555</v>
+        <v>1.509306192</v>
       </c>
       <c r="Q17">
-        <v>1.533299555</v>
+        <v>1.511306192</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1046274358989093</v>
+        <v>0.1052673282400867</v>
       </c>
       <c r="T17">
-        <v>1.179117122490182</v>
+        <v>1.191942906998777</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.641701998916673</v>
+        <v>5.289095623984381</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09638775572167282</v>
+        <v>0.09637669092927273</v>
       </c>
       <c r="C18">
-        <v>37.25593700395432</v>
+        <v>36.82217454200654</v>
       </c>
       <c r="D18">
-        <v>37.19633700395431</v>
+        <v>37.20447454200654</v>
       </c>
       <c r="E18">
-        <v>4.280399999999999</v>
+        <v>4.7223</v>
       </c>
       <c r="F18">
-        <v>7.070399999999999</v>
+        <v>7.5123</v>
       </c>
       <c r="G18">
         <v>7.13</v>
@@ -2763,28 +2763,28 @@
         <v>2.068</v>
       </c>
       <c r="M18">
-        <v>0.39099312</v>
+        <v>0.41543019</v>
       </c>
       <c r="N18">
-        <v>1.67700688</v>
+        <v>1.65256981</v>
       </c>
       <c r="O18">
-        <v>0.167700688</v>
+        <v>0.165256981</v>
       </c>
       <c r="P18">
-        <v>1.509306192</v>
+        <v>1.487312829</v>
       </c>
       <c r="Q18">
-        <v>1.511306192</v>
+        <v>1.489312829</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1052673282400867</v>
+        <v>0.1059226396738226</v>
       </c>
       <c r="T18">
-        <v>1.191942906998777</v>
+        <v>1.205077746555772</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.289095623984381</v>
+        <v>4.977972351985301</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09637669092927273</v>
+        <v>0.09636562613687265</v>
       </c>
       <c r="C19">
-        <v>36.82217454200654</v>
+        <v>36.38841564137802</v>
       </c>
       <c r="D19">
-        <v>37.20447454200654</v>
+        <v>37.21261564137802</v>
       </c>
       <c r="E19">
-        <v>4.7223</v>
+        <v>5.1642</v>
       </c>
       <c r="F19">
-        <v>7.5123</v>
+        <v>7.9542</v>
       </c>
       <c r="G19">
         <v>7.13</v>
@@ -2845,28 +2845,28 @@
         <v>2.068</v>
       </c>
       <c r="M19">
-        <v>0.41543019</v>
+        <v>0.43986726</v>
       </c>
       <c r="N19">
-        <v>1.65256981</v>
+        <v>1.62813274</v>
       </c>
       <c r="O19">
-        <v>0.165256981</v>
+        <v>0.162813274</v>
       </c>
       <c r="P19">
-        <v>1.487312829</v>
+        <v>1.465319466</v>
       </c>
       <c r="Q19">
-        <v>1.489312829</v>
+        <v>1.467319466</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1059226396738226</v>
+        <v>0.1065939343132593</v>
       </c>
       <c r="T19">
-        <v>1.205077746555772</v>
+        <v>1.218532948053181</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.977972351985301</v>
+        <v>4.701418332430561</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09636562613687266</v>
+        <v>0.09678206134447259</v>
       </c>
       <c r="C20">
-        <v>36.38841564137801</v>
+        <v>35.64255297468145</v>
       </c>
       <c r="D20">
-        <v>37.21261564137801</v>
+        <v>36.90865297468144</v>
       </c>
       <c r="E20">
-        <v>5.164199999999999</v>
+        <v>5.606099999999999</v>
       </c>
       <c r="F20">
-        <v>7.954199999999999</v>
+        <v>8.396099999999999</v>
       </c>
       <c r="G20">
         <v>7.13</v>
@@ -2927,45 +2927,45 @@
         <v>2.068</v>
       </c>
       <c r="M20">
-        <v>0.43986726</v>
+        <v>0.48529458</v>
       </c>
       <c r="N20">
-        <v>1.62813274</v>
+        <v>1.58270542</v>
       </c>
       <c r="O20">
-        <v>0.162813274</v>
+        <v>0.158270542</v>
       </c>
       <c r="P20">
-        <v>1.465319466</v>
+        <v>1.424434878</v>
       </c>
       <c r="Q20">
-        <v>1.467319466</v>
+        <v>1.426434878</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1065939343132593</v>
+        <v>0.1072818041289785</v>
       </c>
       <c r="T20">
-        <v>1.218532948053181</v>
+        <v>1.232320376748058</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.701418332430562</v>
+        <v>4.261329273448717</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09678206134447259</v>
+        <v>0.09679349655207252</v>
       </c>
       <c r="C21">
-        <v>35.64255297468145</v>
+        <v>35.19237627005171</v>
       </c>
       <c r="D21">
-        <v>36.90865297468144</v>
+        <v>36.90037627005171</v>
       </c>
       <c r="E21">
-        <v>5.606099999999999</v>
+        <v>6.047999999999999</v>
       </c>
       <c r="F21">
-        <v>8.396099999999999</v>
+        <v>8.837999999999999</v>
       </c>
       <c r="G21">
         <v>7.13</v>
@@ -3009,28 +3009,28 @@
         <v>2.068</v>
       </c>
       <c r="M21">
-        <v>0.48529458</v>
+        <v>0.5108364</v>
       </c>
       <c r="N21">
-        <v>1.58270542</v>
+        <v>1.5571636</v>
       </c>
       <c r="O21">
-        <v>0.158270542</v>
+        <v>0.15571636</v>
       </c>
       <c r="P21">
-        <v>1.424434878</v>
+        <v>1.40144724</v>
       </c>
       <c r="Q21">
-        <v>1.426434878</v>
+        <v>1.40344724</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1072818041289785</v>
+        <v>0.1079868706900906</v>
       </c>
       <c r="T21">
-        <v>1.232320376748058</v>
+        <v>1.246452491160306</v>
       </c>
       <c r="U21">
         <v>0.0578</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.261329273448717</v>
+        <v>4.048262809776281</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09679349655207252</v>
+        <v>0.09746643175967244</v>
       </c>
       <c r="C22">
-        <v>35.19237627005171</v>
+        <v>34.26986320040319</v>
       </c>
       <c r="D22">
-        <v>36.90037627005171</v>
+        <v>36.41976320040318</v>
       </c>
       <c r="E22">
-        <v>6.047999999999999</v>
+        <v>6.4899</v>
       </c>
       <c r="F22">
-        <v>8.837999999999999</v>
+        <v>9.2799</v>
       </c>
       <c r="G22">
         <v>7.13</v>
@@ -3091,45 +3091,45 @@
         <v>2.068</v>
       </c>
       <c r="M22">
-        <v>0.5108364</v>
+        <v>0.56885787</v>
       </c>
       <c r="N22">
-        <v>1.5571636</v>
+        <v>1.49914213</v>
       </c>
       <c r="O22">
-        <v>0.15571636</v>
+        <v>0.149914213</v>
       </c>
       <c r="P22">
-        <v>1.40144724</v>
+        <v>1.349227917</v>
       </c>
       <c r="Q22">
-        <v>1.40344724</v>
+        <v>1.351227917</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1079868706900906</v>
+        <v>0.10870978703756</v>
       </c>
       <c r="T22">
-        <v>1.246452491160306</v>
+        <v>1.260942380620966</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.1</v>
       </c>
       <c r="W22">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.048262809776281</v>
+        <v>3.635354469122489</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09746643175967244</v>
+        <v>0.09806376696727237</v>
       </c>
       <c r="C23">
-        <v>34.26986320040319</v>
+        <v>33.41171293612973</v>
       </c>
       <c r="D23">
-        <v>36.41976320040318</v>
+        <v>36.00351293612973</v>
       </c>
       <c r="E23">
-        <v>6.4899</v>
+        <v>6.9318</v>
       </c>
       <c r="F23">
-        <v>9.2799</v>
+        <v>9.7218</v>
       </c>
       <c r="G23">
         <v>7.13</v>
@@ -3173,45 +3173,45 @@
         <v>2.068</v>
       </c>
       <c r="M23">
-        <v>0.56885787</v>
+        <v>0.62316738</v>
       </c>
       <c r="N23">
-        <v>1.49914213</v>
+        <v>1.44483262</v>
       </c>
       <c r="O23">
-        <v>0.149914213</v>
+        <v>0.144483262</v>
       </c>
       <c r="P23">
-        <v>1.349227917</v>
+        <v>1.300349358</v>
       </c>
       <c r="Q23">
-        <v>1.351227917</v>
+        <v>1.302349358</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.10870978703756</v>
+        <v>0.1094512397016312</v>
       </c>
       <c r="T23">
-        <v>1.260942380620966</v>
+        <v>1.275803805708822</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.1</v>
       </c>
       <c r="W23">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.635354469122489</v>
+        <v>3.318530568785548</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09806376696727237</v>
+        <v>0.0981319021748723</v>
       </c>
       <c r="C24">
-        <v>33.41171293612973</v>
+        <v>32.9229370014459</v>
       </c>
       <c r="D24">
-        <v>36.00351293612973</v>
+        <v>35.95663700144589</v>
       </c>
       <c r="E24">
-        <v>6.9318</v>
+        <v>7.3737</v>
       </c>
       <c r="F24">
-        <v>9.7218</v>
+        <v>10.1637</v>
       </c>
       <c r="G24">
         <v>7.13</v>
@@ -3255,28 +3255,28 @@
         <v>2.068</v>
       </c>
       <c r="M24">
-        <v>0.62316738</v>
+        <v>0.6514931700000001</v>
       </c>
       <c r="N24">
-        <v>1.44483262</v>
+        <v>1.41650683</v>
       </c>
       <c r="O24">
-        <v>0.144483262</v>
+        <v>0.141650683</v>
       </c>
       <c r="P24">
-        <v>1.300349358</v>
+        <v>1.274856147</v>
       </c>
       <c r="Q24">
-        <v>1.302349358</v>
+        <v>1.276856147</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1094512397016312</v>
+        <v>0.1102119508764575</v>
       </c>
       <c r="T24">
-        <v>1.275803805708822</v>
+        <v>1.291051241837921</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.318530568785548</v>
+        <v>3.174246631012263</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0981319021748723</v>
+        <v>0.09820003738247221</v>
       </c>
       <c r="C25">
-        <v>32.9229370014459</v>
+        <v>32.43428297131409</v>
       </c>
       <c r="D25">
-        <v>35.95663700144589</v>
+        <v>35.90988297131409</v>
       </c>
       <c r="E25">
-        <v>7.3737</v>
+        <v>7.815600000000001</v>
       </c>
       <c r="F25">
-        <v>10.1637</v>
+        <v>10.6056</v>
       </c>
       <c r="G25">
         <v>7.13</v>
@@ -3337,28 +3337,28 @@
         <v>2.068</v>
       </c>
       <c r="M25">
-        <v>0.6514931700000001</v>
+        <v>0.6798189600000001</v>
       </c>
       <c r="N25">
-        <v>1.41650683</v>
+        <v>1.38818104</v>
       </c>
       <c r="O25">
-        <v>0.141650683</v>
+        <v>0.138818104</v>
       </c>
       <c r="P25">
-        <v>1.274856147</v>
+        <v>1.249362936</v>
       </c>
       <c r="Q25">
-        <v>1.276856147</v>
+        <v>1.251362936</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1102119508764575</v>
+        <v>0.1109926807664108</v>
       </c>
       <c r="T25">
-        <v>1.291051241837921</v>
+        <v>1.306699926286207</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.174246631012263</v>
+        <v>3.041986354720086</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09820003738247221</v>
+        <v>0.1000231725900722</v>
       </c>
       <c r="C26">
-        <v>32.43428297131409</v>
+        <v>30.78499194606481</v>
       </c>
       <c r="D26">
-        <v>35.90988297131409</v>
+        <v>34.7024919460648</v>
       </c>
       <c r="E26">
-        <v>7.815599999999999</v>
+        <v>8.2575</v>
       </c>
       <c r="F26">
-        <v>10.6056</v>
+        <v>11.0475</v>
       </c>
       <c r="G26">
         <v>7.13</v>
@@ -3419,45 +3419,45 @@
         <v>2.068</v>
       </c>
       <c r="M26">
-        <v>0.67981896</v>
+        <v>0.79431525</v>
       </c>
       <c r="N26">
-        <v>1.38818104</v>
+        <v>1.27368475</v>
       </c>
       <c r="O26">
-        <v>0.138818104</v>
+        <v>0.127368475</v>
       </c>
       <c r="P26">
-        <v>1.249362936</v>
+        <v>1.146316275</v>
       </c>
       <c r="Q26">
-        <v>1.251362936</v>
+        <v>1.148316275</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1109926807664108</v>
+        <v>0.1117942301200962</v>
       </c>
       <c r="T26">
-        <v>1.306699926286207</v>
+        <v>1.322765908986447</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.041986354720086</v>
+        <v>2.603500310487555</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1000231725900722</v>
+        <v>0.1001615077976721</v>
       </c>
       <c r="C27">
-        <v>30.78499194606481</v>
+        <v>30.25478357085452</v>
       </c>
       <c r="D27">
-        <v>34.7024919460648</v>
+        <v>34.61418357085451</v>
       </c>
       <c r="E27">
-        <v>8.2575</v>
+        <v>8.699400000000001</v>
       </c>
       <c r="F27">
-        <v>11.0475</v>
+        <v>11.4894</v>
       </c>
       <c r="G27">
         <v>7.13</v>
@@ -3501,28 +3501,28 @@
         <v>2.068</v>
       </c>
       <c r="M27">
-        <v>0.79431525</v>
+        <v>0.82608786</v>
       </c>
       <c r="N27">
-        <v>1.27368475</v>
+        <v>1.24191214</v>
       </c>
       <c r="O27">
-        <v>0.127368475</v>
+        <v>0.124191214</v>
       </c>
       <c r="P27">
-        <v>1.146316275</v>
+        <v>1.117720926</v>
       </c>
       <c r="Q27">
-        <v>1.148316275</v>
+        <v>1.119720926</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1117942301200962</v>
+        <v>0.1126174429698271</v>
       </c>
       <c r="T27">
-        <v>1.322765908986447</v>
+        <v>1.339266107435343</v>
       </c>
       <c r="U27">
         <v>0.07190000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.603500310487555</v>
+        <v>2.503365683161111</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1001615077976721</v>
+        <v>0.101247543005272</v>
       </c>
       <c r="C28">
-        <v>30.25478357085452</v>
+        <v>29.13490543146788</v>
       </c>
       <c r="D28">
-        <v>34.61418357085451</v>
+        <v>33.93620543146788</v>
       </c>
       <c r="E28">
-        <v>8.699400000000001</v>
+        <v>9.141300000000001</v>
       </c>
       <c r="F28">
-        <v>11.4894</v>
+        <v>11.9313</v>
       </c>
       <c r="G28">
         <v>7.13</v>
@@ -3583,45 +3583,45 @@
         <v>2.068</v>
       </c>
       <c r="M28">
-        <v>0.82608786</v>
+        <v>0.9043925400000001</v>
       </c>
       <c r="N28">
-        <v>1.24191214</v>
+        <v>1.16360746</v>
       </c>
       <c r="O28">
-        <v>0.124191214</v>
+        <v>0.116360746</v>
       </c>
       <c r="P28">
-        <v>1.117720926</v>
+        <v>1.047246714</v>
       </c>
       <c r="Q28">
-        <v>1.119720926</v>
+        <v>1.049246714</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1126174429698271</v>
+        <v>0.113463209596263</v>
       </c>
       <c r="T28">
-        <v>1.339266107435343</v>
+        <v>1.356218366115715</v>
       </c>
       <c r="U28">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.1</v>
       </c>
       <c r="W28">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.503365683161111</v>
+        <v>2.286617711375638</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.101247543005272</v>
+        <v>0.1014209782128719</v>
       </c>
       <c r="C29">
-        <v>29.13490543146788</v>
+        <v>28.58718685323945</v>
       </c>
       <c r="D29">
-        <v>33.93620543146788</v>
+        <v>33.83038685323945</v>
       </c>
       <c r="E29">
-        <v>9.141300000000001</v>
+        <v>9.583200000000001</v>
       </c>
       <c r="F29">
-        <v>11.9313</v>
+        <v>12.3732</v>
       </c>
       <c r="G29">
         <v>7.13</v>
@@ -3665,28 +3665,28 @@
         <v>2.068</v>
       </c>
       <c r="M29">
-        <v>0.9043925400000001</v>
+        <v>0.9378885600000001</v>
       </c>
       <c r="N29">
-        <v>1.16360746</v>
+        <v>1.13011144</v>
       </c>
       <c r="O29">
-        <v>0.116360746</v>
+        <v>0.113011144</v>
       </c>
       <c r="P29">
-        <v>1.047246714</v>
+        <v>1.017100296</v>
       </c>
       <c r="Q29">
-        <v>1.049246714</v>
+        <v>1.019100296</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.113463209596263</v>
+        <v>0.1143324697400999</v>
       </c>
       <c r="T29">
-        <v>1.356218366115715</v>
+        <v>1.373641520870542</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.286617711375638</v>
+        <v>2.204952793112222</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1014209782128719</v>
+        <v>0.1015944134204719</v>
       </c>
       <c r="C30">
-        <v>28.58718685323945</v>
+        <v>28.04012614256291</v>
       </c>
       <c r="D30">
-        <v>33.83038685323945</v>
+        <v>33.72522614256291</v>
       </c>
       <c r="E30">
-        <v>9.583200000000001</v>
+        <v>10.0251</v>
       </c>
       <c r="F30">
-        <v>12.3732</v>
+        <v>12.8151</v>
       </c>
       <c r="G30">
         <v>7.13</v>
@@ -3747,28 +3747,28 @@
         <v>2.068</v>
       </c>
       <c r="M30">
-        <v>0.9378885600000001</v>
+        <v>0.9713845800000002</v>
       </c>
       <c r="N30">
-        <v>1.13011144</v>
+        <v>1.09661542</v>
       </c>
       <c r="O30">
-        <v>0.113011144</v>
+        <v>0.109661542</v>
       </c>
       <c r="P30">
-        <v>1.017100296</v>
+        <v>0.986953878</v>
       </c>
       <c r="Q30">
-        <v>1.019100296</v>
+        <v>0.988953878</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1143324697400999</v>
+        <v>0.1152262160851716</v>
       </c>
       <c r="T30">
-        <v>1.373641520870542</v>
+        <v>1.391555468717054</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.204952793112222</v>
+        <v>2.128919938177318</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1015944134204718</v>
+        <v>0.1017678486280718</v>
       </c>
       <c r="C31">
-        <v>28.04012614256292</v>
+        <v>27.49371718356649</v>
       </c>
       <c r="D31">
-        <v>33.72522614256292</v>
+        <v>33.62071718356648</v>
       </c>
       <c r="E31">
-        <v>10.0251</v>
+        <v>10.467</v>
       </c>
       <c r="F31">
-        <v>12.8151</v>
+        <v>13.257</v>
       </c>
       <c r="G31">
         <v>7.13</v>
@@ -3829,28 +3829,28 @@
         <v>2.068</v>
       </c>
       <c r="M31">
-        <v>0.9713845800000001</v>
+        <v>1.0048806</v>
       </c>
       <c r="N31">
-        <v>1.09661542</v>
+        <v>1.0631194</v>
       </c>
       <c r="O31">
-        <v>0.109661542</v>
+        <v>0.10631194</v>
       </c>
       <c r="P31">
-        <v>0.986953878</v>
+        <v>0.9568074599999999</v>
       </c>
       <c r="Q31">
-        <v>0.988953878</v>
+        <v>0.9588074599999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1152262160851716</v>
+        <v>0.1161454980401025</v>
       </c>
       <c r="T31">
-        <v>1.391555468717053</v>
+        <v>1.409981243644894</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.128919938177318</v>
+        <v>2.057955940238074</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1017678486280718</v>
+        <v>0.1059030838356717</v>
       </c>
       <c r="C32">
-        <v>27.49371718356649</v>
+        <v>24.73863182718167</v>
       </c>
       <c r="D32">
-        <v>33.62071718356648</v>
+        <v>31.30753182718167</v>
       </c>
       <c r="E32">
-        <v>10.467</v>
+        <v>10.9089</v>
       </c>
       <c r="F32">
-        <v>13.257</v>
+        <v>13.6989</v>
       </c>
       <c r="G32">
         <v>7.13</v>
@@ -3911,45 +3911,45 @@
         <v>2.068</v>
       </c>
       <c r="M32">
-        <v>1.0048806</v>
+        <v>1.232901</v>
       </c>
       <c r="N32">
-        <v>1.0631194</v>
+        <v>0.835099</v>
       </c>
       <c r="O32">
-        <v>0.10631194</v>
+        <v>0.08350990000000001</v>
       </c>
       <c r="P32">
-        <v>0.9568074599999999</v>
+        <v>0.7515891</v>
       </c>
       <c r="Q32">
-        <v>0.9588074599999999</v>
+        <v>0.7535891</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1161454980401025</v>
+        <v>0.1170914258487996</v>
       </c>
       <c r="T32">
-        <v>1.409981243644894</v>
+        <v>1.428941099005427</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.057955940238074</v>
+        <v>1.677344734086516</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1059030838356717</v>
+        <v>0.1062043190432716</v>
       </c>
       <c r="C33">
-        <v>24.73863182718167</v>
+        <v>24.14060175239933</v>
       </c>
       <c r="D33">
-        <v>31.30753182718167</v>
+        <v>31.15140175239933</v>
       </c>
       <c r="E33">
-        <v>10.9089</v>
+        <v>11.3508</v>
       </c>
       <c r="F33">
-        <v>13.6989</v>
+        <v>14.1408</v>
       </c>
       <c r="G33">
         <v>7.13</v>
@@ -3993,28 +3993,28 @@
         <v>2.068</v>
       </c>
       <c r="M33">
-        <v>1.232901</v>
+        <v>1.272672</v>
       </c>
       <c r="N33">
-        <v>0.835099</v>
+        <v>0.7953280000000003</v>
       </c>
       <c r="O33">
-        <v>0.08350990000000001</v>
+        <v>0.07953280000000003</v>
       </c>
       <c r="P33">
-        <v>0.7515891</v>
+        <v>0.7157952000000002</v>
       </c>
       <c r="Q33">
-        <v>0.7535891</v>
+        <v>0.7177952000000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1170914258487996</v>
+        <v>0.1180651750636348</v>
       </c>
       <c r="T33">
-        <v>1.428941099005427</v>
+        <v>1.44845859717068</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.677344734086516</v>
+        <v>1.624927711146313</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1062043190432716</v>
+        <v>0.1065055542508716</v>
       </c>
       <c r="C34">
-        <v>24.14060175239933</v>
+        <v>23.54412118576563</v>
       </c>
       <c r="D34">
-        <v>31.15140175239933</v>
+        <v>30.99682118576563</v>
       </c>
       <c r="E34">
-        <v>11.3508</v>
+        <v>11.7927</v>
       </c>
       <c r="F34">
-        <v>14.1408</v>
+        <v>14.5827</v>
       </c>
       <c r="G34">
         <v>7.13</v>
@@ -4075,28 +4075,28 @@
         <v>2.068</v>
       </c>
       <c r="M34">
-        <v>1.272672</v>
+        <v>1.312443</v>
       </c>
       <c r="N34">
-        <v>0.7953280000000003</v>
+        <v>0.7555570000000003</v>
       </c>
       <c r="O34">
-        <v>0.07953280000000003</v>
+        <v>0.07555570000000003</v>
       </c>
       <c r="P34">
-        <v>0.7157952000000002</v>
+        <v>0.6800013000000003</v>
       </c>
       <c r="Q34">
-        <v>0.7177952000000002</v>
+        <v>0.6820013000000003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1180651750636348</v>
+        <v>0.1190679914192113</v>
       </c>
       <c r="T34">
-        <v>1.44845859717068</v>
+        <v>1.468558707221463</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.624927711146313</v>
+        <v>1.575687477475213</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1065055542508716</v>
+        <v>0.1068067894584715</v>
       </c>
       <c r="C35">
-        <v>23.54412118576563</v>
+        <v>22.94916717411028</v>
       </c>
       <c r="D35">
-        <v>30.99682118576563</v>
+        <v>30.84376717411028</v>
       </c>
       <c r="E35">
-        <v>11.7927</v>
+        <v>12.2346</v>
       </c>
       <c r="F35">
-        <v>14.5827</v>
+        <v>15.0246</v>
       </c>
       <c r="G35">
         <v>7.13</v>
@@ -4157,28 +4157,28 @@
         <v>2.068</v>
       </c>
       <c r="M35">
-        <v>1.312443</v>
+        <v>1.352214</v>
       </c>
       <c r="N35">
-        <v>0.7555570000000003</v>
+        <v>0.7157860000000003</v>
       </c>
       <c r="O35">
-        <v>0.07555570000000003</v>
+        <v>0.07157860000000003</v>
       </c>
       <c r="P35">
-        <v>0.6800013000000003</v>
+        <v>0.6442074000000002</v>
       </c>
       <c r="Q35">
-        <v>0.6820013000000003</v>
+        <v>0.6462074000000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1190679914192113</v>
+        <v>0.1201011961491992</v>
       </c>
       <c r="T35">
-        <v>1.468558707221463</v>
+        <v>1.48926791151621</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.575687477475213</v>
+        <v>1.529343728137706</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1068067894584715</v>
+        <v>0.1256166854719874</v>
       </c>
       <c r="C36">
-        <v>22.94916717411028</v>
+        <v>15.23851065059208</v>
       </c>
       <c r="D36">
-        <v>30.84376717411028</v>
+        <v>23.57501065059208</v>
       </c>
       <c r="E36">
-        <v>12.2346</v>
+        <v>12.6765</v>
       </c>
       <c r="F36">
-        <v>15.0246</v>
+        <v>15.4665</v>
       </c>
       <c r="G36">
         <v>7.13</v>
@@ -4239,45 +4239,45 @@
         <v>2.068</v>
       </c>
       <c r="M36">
-        <v>1.352214</v>
+        <v>2.2704822</v>
       </c>
       <c r="N36">
-        <v>0.7157860000000003</v>
+        <v>-0.2024821999999999</v>
       </c>
       <c r="O36">
-        <v>0.07157860000000003</v>
+        <v>-0.02024822</v>
       </c>
       <c r="P36">
-        <v>0.6442074000000002</v>
+        <v>-0.18223398</v>
       </c>
       <c r="Q36">
-        <v>0.6462074000000002</v>
+        <v>-0.18023398</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1201011961491992</v>
+        <v>0.1214099650462904</v>
       </c>
       <c r="T36">
-        <v>1.48926791151621</v>
+        <v>1.515500430278283</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.1</v>
+        <v>0.0910819736882324</v>
       </c>
       <c r="W36">
-        <v>0.081</v>
+        <v>0.1334291662625675</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.529343728137706</v>
+        <v>0.910819736882324</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1256166854719874</v>
+        <v>0.1266266854719874</v>
       </c>
       <c r="C37">
-        <v>15.23851065059208</v>
+        <v>14.50202031055704</v>
       </c>
       <c r="D37">
-        <v>23.57501065059208</v>
+        <v>23.28042031055704</v>
       </c>
       <c r="E37">
-        <v>12.6765</v>
+        <v>13.1184</v>
       </c>
       <c r="F37">
-        <v>15.4665</v>
+        <v>15.9084</v>
       </c>
       <c r="G37">
         <v>7.13</v>
@@ -4321,37 +4321,37 @@
         <v>2.068</v>
       </c>
       <c r="M37">
-        <v>2.2704822</v>
+        <v>2.33535312</v>
       </c>
       <c r="N37">
-        <v>-0.2024821999999999</v>
+        <v>-0.2673531200000001</v>
       </c>
       <c r="O37">
-        <v>-0.02024822</v>
+        <v>-0.02673531200000001</v>
       </c>
       <c r="P37">
-        <v>-0.18223398</v>
+        <v>-0.2406178080000001</v>
       </c>
       <c r="Q37">
-        <v>-0.18023398</v>
+        <v>-0.2386178080000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1214099650462904</v>
+        <v>0.1225913707501387</v>
       </c>
       <c r="T37">
-        <v>1.515500430278283</v>
+        <v>1.539180124501381</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.0910819736882324</v>
+        <v>0.08855191886355927</v>
       </c>
       <c r="W37">
-        <v>0.1334291662625675</v>
+        <v>0.1338005783108295</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.910819736882324</v>
+        <v>0.8855191886355926</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1266266854719874</v>
+        <v>0.1276366854719874</v>
       </c>
       <c r="C38">
-        <v>14.50202031055703</v>
+        <v>13.77280143421139</v>
       </c>
       <c r="D38">
-        <v>23.28042031055703</v>
+        <v>22.99310143421139</v>
       </c>
       <c r="E38">
-        <v>13.1184</v>
+        <v>13.5603</v>
       </c>
       <c r="F38">
-        <v>15.9084</v>
+        <v>16.3503</v>
       </c>
       <c r="G38">
         <v>7.13</v>
@@ -4403,37 +4403,37 @@
         <v>2.068</v>
       </c>
       <c r="M38">
-        <v>2.33535312</v>
+        <v>2.40022404</v>
       </c>
       <c r="N38">
-        <v>-0.2673531200000001</v>
+        <v>-0.3322240400000003</v>
       </c>
       <c r="O38">
-        <v>-0.02673531200000001</v>
+        <v>-0.03322240400000003</v>
       </c>
       <c r="P38">
-        <v>-0.2406178080000001</v>
+        <v>-0.2990016360000002</v>
       </c>
       <c r="Q38">
-        <v>-0.2386178080000001</v>
+        <v>-0.2970016360000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1225913707501387</v>
+        <v>0.1238102813969663</v>
       </c>
       <c r="T38">
-        <v>1.539180124501381</v>
+        <v>1.563611555049023</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.08855191886355927</v>
+        <v>0.08615862375913874</v>
       </c>
       <c r="W38">
-        <v>0.1338005783108295</v>
+        <v>0.1341519140321585</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8855191886355926</v>
+        <v>0.8615862375913874</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1276366854719874</v>
+        <v>0.1286466854719874</v>
       </c>
       <c r="C39">
-        <v>13.77280143421139</v>
+        <v>13.05058807808557</v>
       </c>
       <c r="D39">
-        <v>22.99310143421139</v>
+        <v>22.71278807808557</v>
       </c>
       <c r="E39">
-        <v>13.5603</v>
+        <v>14.0022</v>
       </c>
       <c r="F39">
-        <v>16.3503</v>
+        <v>16.7922</v>
       </c>
       <c r="G39">
         <v>7.13</v>
@@ -4485,37 +4485,37 @@
         <v>2.068</v>
       </c>
       <c r="M39">
-        <v>2.40022404</v>
+        <v>2.46509496</v>
       </c>
       <c r="N39">
-        <v>-0.3322240400000003</v>
+        <v>-0.39709496</v>
       </c>
       <c r="O39">
-        <v>-0.03322240400000003</v>
+        <v>-0.039709496</v>
       </c>
       <c r="P39">
-        <v>-0.2990016360000002</v>
+        <v>-0.357385464</v>
       </c>
       <c r="Q39">
-        <v>-0.2970016360000002</v>
+        <v>-0.355385464</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1238102813969663</v>
+        <v>0.1250685117420786</v>
       </c>
       <c r="T39">
-        <v>1.563611555049023</v>
+        <v>1.58883109625949</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.08615862375913874</v>
+        <v>0.0838912915549509</v>
       </c>
       <c r="W39">
-        <v>0.1341519140321585</v>
+        <v>0.1344847583997332</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8615862375913874</v>
+        <v>0.8389129155495089</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1286466854719874</v>
+        <v>0.1296566854719874</v>
       </c>
       <c r="C40">
-        <v>13.05058807808557</v>
+        <v>12.33512711118414</v>
       </c>
       <c r="D40">
-        <v>22.71278807808557</v>
+        <v>22.43922711118414</v>
       </c>
       <c r="E40">
-        <v>14.0022</v>
+        <v>14.4441</v>
       </c>
       <c r="F40">
-        <v>16.7922</v>
+        <v>17.2341</v>
       </c>
       <c r="G40">
         <v>7.13</v>
@@ -4567,37 +4567,37 @@
         <v>2.068</v>
       </c>
       <c r="M40">
-        <v>2.46509496</v>
+        <v>2.52996588</v>
       </c>
       <c r="N40">
-        <v>-0.39709496</v>
+        <v>-0.4619658799999997</v>
       </c>
       <c r="O40">
-        <v>-0.039709496</v>
+        <v>-0.04619658799999998</v>
       </c>
       <c r="P40">
-        <v>-0.357385464</v>
+        <v>-0.4157692919999997</v>
       </c>
       <c r="Q40">
-        <v>-0.355385464</v>
+        <v>-0.4137692919999997</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1250685117420786</v>
+        <v>0.1263679955411291</v>
       </c>
       <c r="T40">
-        <v>1.58883109625949</v>
+        <v>1.614877507673581</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.0838912915549509</v>
+        <v>0.08174023279713165</v>
       </c>
       <c r="W40">
-        <v>0.1344847583997332</v>
+        <v>0.1348005338253811</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8389129155495089</v>
+        <v>0.8174023279713165</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1296566854719874</v>
+        <v>0.1527018897373221</v>
       </c>
       <c r="C41">
-        <v>12.33512711118414</v>
+        <v>7.055926539565373</v>
       </c>
       <c r="D41">
-        <v>22.43922711118414</v>
+        <v>17.60192653956537</v>
       </c>
       <c r="E41">
-        <v>14.4441</v>
+        <v>14.886</v>
       </c>
       <c r="F41">
-        <v>17.2341</v>
+        <v>17.676</v>
       </c>
       <c r="G41">
         <v>7.13</v>
@@ -4649,45 +4649,45 @@
         <v>2.068</v>
       </c>
       <c r="M41">
-        <v>2.52996588</v>
+        <v>3.5493408</v>
       </c>
       <c r="N41">
-        <v>-0.4619658799999997</v>
+        <v>-1.4813408</v>
       </c>
       <c r="O41">
-        <v>-0.04619658799999998</v>
+        <v>-0.14813408</v>
       </c>
       <c r="P41">
-        <v>-0.4157692919999997</v>
+        <v>-1.33320672</v>
       </c>
       <c r="Q41">
-        <v>-0.4137692919999997</v>
+        <v>-1.33120672</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1263679955411291</v>
+        <v>0.128436135909039</v>
       </c>
       <c r="T41">
-        <v>1.614877507673581</v>
+        <v>1.656330609993156</v>
       </c>
       <c r="U41">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.08174023279713165</v>
+        <v>0.05826434024030604</v>
       </c>
       <c r="W41">
-        <v>0.1348005338253811</v>
+        <v>0.1891005204797466</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8174023279713165</v>
+        <v>0.5826434024030603</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1527018897373221</v>
+        <v>0.1542518897373221</v>
       </c>
       <c r="C42">
-        <v>7.055926539565373</v>
+        <v>6.362458897891191</v>
       </c>
       <c r="D42">
-        <v>17.60192653956537</v>
+        <v>17.35035889789119</v>
       </c>
       <c r="E42">
-        <v>14.886</v>
+        <v>15.3279</v>
       </c>
       <c r="F42">
-        <v>17.676</v>
+        <v>18.1179</v>
       </c>
       <c r="G42">
         <v>7.13</v>
@@ -4731,37 +4731,37 @@
         <v>2.068</v>
       </c>
       <c r="M42">
-        <v>3.5493408</v>
+        <v>3.63807432</v>
       </c>
       <c r="N42">
-        <v>-1.4813408</v>
+        <v>-1.57007432</v>
       </c>
       <c r="O42">
-        <v>-0.14813408</v>
+        <v>-0.157007432</v>
       </c>
       <c r="P42">
-        <v>-1.33320672</v>
+        <v>-1.413066888</v>
       </c>
       <c r="Q42">
-        <v>-1.33120672</v>
+        <v>-1.411066888</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.128436135909039</v>
+        <v>0.1298367483820736</v>
       </c>
       <c r="T42">
-        <v>1.656330609993156</v>
+        <v>1.684404010162532</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05826434024030604</v>
+        <v>0.05684325877103028</v>
       </c>
       <c r="W42">
-        <v>0.1891005204797466</v>
+        <v>0.1893858736387771</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5826434024030603</v>
+        <v>0.5684325877103028</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1542518897373221</v>
+        <v>0.1558018897373221</v>
       </c>
       <c r="C43">
-        <v>6.362458897891191</v>
+        <v>5.676080767961331</v>
       </c>
       <c r="D43">
-        <v>17.35035889789119</v>
+        <v>17.10588076796133</v>
       </c>
       <c r="E43">
-        <v>15.3279</v>
+        <v>15.7698</v>
       </c>
       <c r="F43">
-        <v>18.1179</v>
+        <v>18.5598</v>
       </c>
       <c r="G43">
         <v>7.13</v>
@@ -4813,37 +4813,37 @@
         <v>2.068</v>
       </c>
       <c r="M43">
-        <v>3.63807432</v>
+        <v>3.72680784</v>
       </c>
       <c r="N43">
-        <v>-1.57007432</v>
+        <v>-1.65880784</v>
       </c>
       <c r="O43">
-        <v>-0.157007432</v>
+        <v>-0.165880784</v>
       </c>
       <c r="P43">
-        <v>-1.413066888</v>
+        <v>-1.492927056</v>
       </c>
       <c r="Q43">
-        <v>-1.411066888</v>
+        <v>-1.490927056</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1298367483820736</v>
+        <v>0.131285657836937</v>
       </c>
       <c r="T43">
-        <v>1.684404010162532</v>
+        <v>1.71344545861361</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.05684325877103028</v>
+        <v>0.05548984784791051</v>
       </c>
       <c r="W43">
-        <v>0.1893858736387771</v>
+        <v>0.1896576385521396</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5684325877103028</v>
+        <v>0.5548984784791051</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1558018897373221</v>
+        <v>0.1573518897373221</v>
       </c>
       <c r="C44">
-        <v>5.676080767961331</v>
+        <v>4.996496626054149</v>
       </c>
       <c r="D44">
-        <v>17.10588076796133</v>
+        <v>16.86819662605415</v>
       </c>
       <c r="E44">
-        <v>15.7698</v>
+        <v>16.2117</v>
       </c>
       <c r="F44">
-        <v>18.5598</v>
+        <v>19.0017</v>
       </c>
       <c r="G44">
         <v>7.13</v>
@@ -4895,37 +4895,37 @@
         <v>2.068</v>
       </c>
       <c r="M44">
-        <v>3.72680784</v>
+        <v>3.81554136</v>
       </c>
       <c r="N44">
-        <v>-1.65880784</v>
+        <v>-1.74754136</v>
       </c>
       <c r="O44">
-        <v>-0.165880784</v>
+        <v>-0.174754136</v>
       </c>
       <c r="P44">
-        <v>-1.492927056</v>
+        <v>-1.572787224</v>
       </c>
       <c r="Q44">
-        <v>-1.490927056</v>
+        <v>-1.570787224</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1312856578369369</v>
+        <v>0.1327854062200411</v>
       </c>
       <c r="T44">
-        <v>1.713445458613609</v>
+        <v>1.743505905255954</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.05548984784791051</v>
+        <v>0.05419938627005212</v>
       </c>
       <c r="W44">
-        <v>0.1896576385521396</v>
+        <v>0.1899167632369735</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5548984784791051</v>
+        <v>0.5419938627005212</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1573518897373221</v>
+        <v>0.1589018897373221</v>
       </c>
       <c r="C45">
-        <v>4.996496626054149</v>
+        <v>4.323427148416709</v>
       </c>
       <c r="D45">
-        <v>16.86819662605415</v>
+        <v>16.63702714841671</v>
       </c>
       <c r="E45">
-        <v>16.2117</v>
+        <v>16.6536</v>
       </c>
       <c r="F45">
-        <v>19.0017</v>
+        <v>19.4436</v>
       </c>
       <c r="G45">
         <v>7.13</v>
@@ -4977,37 +4977,37 @@
         <v>2.068</v>
       </c>
       <c r="M45">
-        <v>3.81554136</v>
+        <v>3.90427488</v>
       </c>
       <c r="N45">
-        <v>-1.74754136</v>
+        <v>-1.83627488</v>
       </c>
       <c r="O45">
-        <v>-0.174754136</v>
+        <v>-0.183627488</v>
       </c>
       <c r="P45">
-        <v>-1.572787224</v>
+        <v>-1.652647392</v>
       </c>
       <c r="Q45">
-        <v>-1.570787224</v>
+        <v>-1.650647392</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1327854062200411</v>
+        <v>0.134338717045399</v>
       </c>
       <c r="T45">
-        <v>1.743505905255954</v>
+        <v>1.774639939278382</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05419938627005212</v>
+        <v>0.05296758203664185</v>
       </c>
       <c r="W45">
-        <v>0.1899167632369735</v>
+        <v>0.1901641095270423</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5419938627005212</v>
+        <v>0.5296758203664185</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1589018897373221</v>
+        <v>0.1604518897373221</v>
       </c>
       <c r="C46">
-        <v>4.323427148416709</v>
+        <v>3.65660811621299</v>
       </c>
       <c r="D46">
-        <v>16.63702714841671</v>
+        <v>16.41210811621299</v>
       </c>
       <c r="E46">
-        <v>16.6536</v>
+        <v>17.0955</v>
       </c>
       <c r="F46">
-        <v>19.4436</v>
+        <v>19.8855</v>
       </c>
       <c r="G46">
         <v>7.13</v>
@@ -5059,37 +5059,37 @@
         <v>2.068</v>
       </c>
       <c r="M46">
-        <v>3.90427488</v>
+        <v>3.9930084</v>
       </c>
       <c r="N46">
-        <v>-1.83627488</v>
+        <v>-1.9250084</v>
       </c>
       <c r="O46">
-        <v>-0.183627488</v>
+        <v>-0.19250084</v>
       </c>
       <c r="P46">
-        <v>-1.652647392</v>
+        <v>-1.73250756</v>
       </c>
       <c r="Q46">
-        <v>-1.650647392</v>
+        <v>-1.73050756</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.134338717045399</v>
+        <v>0.1359485119007699</v>
       </c>
       <c r="T46">
-        <v>1.774639939278382</v>
+        <v>1.806906119992534</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.05296758203664185</v>
+        <v>0.0517905246580498</v>
       </c>
       <c r="W46">
-        <v>0.1901641095270423</v>
+        <v>0.1904004626486636</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5296758203664185</v>
+        <v>0.5179052465804981</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1604518897373221</v>
+        <v>0.162001889737322</v>
       </c>
       <c r="C47">
-        <v>3.65660811621299</v>
+        <v>2.9957894081125</v>
       </c>
       <c r="D47">
-        <v>16.41210811621299</v>
+        <v>16.1931894081125</v>
       </c>
       <c r="E47">
-        <v>17.0955</v>
+        <v>17.5374</v>
       </c>
       <c r="F47">
-        <v>19.8855</v>
+        <v>20.3274</v>
       </c>
       <c r="G47">
         <v>7.13</v>
@@ -5141,37 +5141,37 @@
         <v>2.068</v>
       </c>
       <c r="M47">
-        <v>3.9930084</v>
+        <v>4.081741920000001</v>
       </c>
       <c r="N47">
-        <v>-1.9250084</v>
+        <v>-2.013741920000001</v>
       </c>
       <c r="O47">
-        <v>-0.19250084</v>
+        <v>-0.2013741920000001</v>
       </c>
       <c r="P47">
-        <v>-1.73250756</v>
+        <v>-1.812367728000001</v>
       </c>
       <c r="Q47">
-        <v>-1.73050756</v>
+        <v>-1.810367728000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1359485119007699</v>
+        <v>0.1376179287878212</v>
       </c>
       <c r="T47">
-        <v>1.806906119992534</v>
+        <v>1.84036734443684</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.0517905246580498</v>
+        <v>0.05066464368722264</v>
       </c>
       <c r="W47">
-        <v>0.1904004626486636</v>
+        <v>0.1906265395476057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5179052465804981</v>
+        <v>0.5066464368722263</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.162001889737322</v>
+        <v>0.1801774999150692</v>
       </c>
       <c r="C48">
-        <v>2.9957894081125</v>
+        <v>0.3636336108079163</v>
       </c>
       <c r="D48">
-        <v>16.1931894081125</v>
+        <v>14.00293361080792</v>
       </c>
       <c r="E48">
-        <v>17.5374</v>
+        <v>17.9793</v>
       </c>
       <c r="F48">
-        <v>20.3274</v>
+        <v>20.7693</v>
       </c>
       <c r="G48">
         <v>7.13</v>
@@ -5223,45 +5223,45 @@
         <v>2.068</v>
       </c>
       <c r="M48">
-        <v>4.081741920000001</v>
+        <v>4.897400940000001</v>
       </c>
       <c r="N48">
-        <v>-2.013741920000001</v>
+        <v>-2.829400940000001</v>
       </c>
       <c r="O48">
-        <v>-0.2013741920000001</v>
+        <v>-0.2829400940000001</v>
       </c>
       <c r="P48">
-        <v>-1.812367728000001</v>
+        <v>-2.546460846</v>
       </c>
       <c r="Q48">
-        <v>-1.810367728000001</v>
+        <v>-2.544460846000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1376179287878212</v>
+        <v>0.1396816824965482</v>
       </c>
       <c r="T48">
-        <v>1.84036734443684</v>
+        <v>1.881732522051317</v>
       </c>
       <c r="U48">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05066464368722264</v>
+        <v>0.04222647941910184</v>
       </c>
       <c r="W48">
-        <v>0.1906265395476057</v>
+        <v>0.2258429961529758</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.5066464368722263</v>
+        <v>0.4222647941910184</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1801774999150692</v>
+        <v>0.1820774999150692</v>
       </c>
       <c r="C49">
-        <v>0.3636336108079163</v>
+        <v>-0.2734972517858054</v>
       </c>
       <c r="D49">
-        <v>14.00293361080792</v>
+        <v>13.8077027482142</v>
       </c>
       <c r="E49">
-        <v>17.9793</v>
+        <v>18.4212</v>
       </c>
       <c r="F49">
-        <v>20.7693</v>
+        <v>21.2112</v>
       </c>
       <c r="G49">
         <v>7.13</v>
@@ -5305,37 +5305,37 @@
         <v>2.068</v>
       </c>
       <c r="M49">
-        <v>4.897400940000001</v>
+        <v>5.00160096</v>
       </c>
       <c r="N49">
-        <v>-2.829400940000001</v>
+        <v>-2.93360096</v>
       </c>
       <c r="O49">
-        <v>-0.2829400940000001</v>
+        <v>-0.293360096</v>
       </c>
       <c r="P49">
-        <v>-2.546460846</v>
+        <v>-2.640240864</v>
       </c>
       <c r="Q49">
-        <v>-2.544460846000001</v>
+        <v>-2.638240864</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1396816824965482</v>
+        <v>0.1414870994676357</v>
       </c>
       <c r="T49">
-        <v>1.881732522051317</v>
+        <v>1.917919685936919</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04222647941910184</v>
+        <v>0.04134676109787055</v>
       </c>
       <c r="W49">
-        <v>0.2258429961529758</v>
+        <v>0.2260504337331221</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4222647941910184</v>
+        <v>0.4134676109787055</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1820774999150692</v>
+        <v>0.1839774999150692</v>
       </c>
       <c r="C50">
-        <v>-0.2734972517858019</v>
+        <v>-0.9052590978731345</v>
       </c>
       <c r="D50">
-        <v>13.8077027482142</v>
+        <v>13.61784090212686</v>
       </c>
       <c r="E50">
-        <v>18.4212</v>
+        <v>18.8631</v>
       </c>
       <c r="F50">
-        <v>21.2112</v>
+        <v>21.6531</v>
       </c>
       <c r="G50">
         <v>7.13</v>
@@ -5387,37 +5387,37 @@
         <v>2.068</v>
       </c>
       <c r="M50">
-        <v>5.001600959999999</v>
+        <v>5.10580098</v>
       </c>
       <c r="N50">
-        <v>-2.933600959999999</v>
+        <v>-3.03780098</v>
       </c>
       <c r="O50">
-        <v>-0.293360096</v>
+        <v>-0.303780098</v>
       </c>
       <c r="P50">
-        <v>-2.640240863999999</v>
+        <v>-2.734020882</v>
       </c>
       <c r="Q50">
-        <v>-2.638240864</v>
+        <v>-2.732020882</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1414870994676357</v>
+        <v>0.143363317104256</v>
       </c>
       <c r="T50">
-        <v>1.917919685936919</v>
+        <v>1.955525954288624</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04134676109787056</v>
+        <v>0.0405029496468936</v>
       </c>
       <c r="W50">
-        <v>0.2260504337331221</v>
+        <v>0.2262494044732625</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4134676109787055</v>
+        <v>0.405029496468936</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1839774999150692</v>
+        <v>0.1858774999150692</v>
       </c>
       <c r="C51">
-        <v>-0.9052590978731345</v>
+        <v>-1.531870402184886</v>
       </c>
       <c r="D51">
-        <v>13.61784090212686</v>
+        <v>13.43312959781511</v>
       </c>
       <c r="E51">
-        <v>18.8631</v>
+        <v>19.305</v>
       </c>
       <c r="F51">
-        <v>21.6531</v>
+        <v>22.095</v>
       </c>
       <c r="G51">
         <v>7.13</v>
@@ -5469,37 +5469,37 @@
         <v>2.068</v>
       </c>
       <c r="M51">
-        <v>5.10580098</v>
+        <v>5.210001</v>
       </c>
       <c r="N51">
-        <v>-3.03780098</v>
+        <v>-3.142001</v>
       </c>
       <c r="O51">
-        <v>-0.303780098</v>
+        <v>-0.3142001</v>
       </c>
       <c r="P51">
-        <v>-2.734020882</v>
+        <v>-2.8278009</v>
       </c>
       <c r="Q51">
-        <v>-2.732020882</v>
+        <v>-2.8258009</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.143363317104256</v>
+        <v>0.1453145834463411</v>
       </c>
       <c r="T51">
-        <v>1.955525954288624</v>
+        <v>1.994636473374396</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0405029496468936</v>
+        <v>0.03969289065395573</v>
       </c>
       <c r="W51">
-        <v>0.2262494044732625</v>
+        <v>0.2264404163837972</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.405029496468936</v>
+        <v>0.3969289065395573</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1858774999150692</v>
+        <v>0.1877774999150692</v>
       </c>
       <c r="C52">
-        <v>-1.531870402184886</v>
+        <v>-2.153537944585029</v>
       </c>
       <c r="D52">
-        <v>13.43312959781511</v>
+        <v>13.25336205541497</v>
       </c>
       <c r="E52">
-        <v>19.305</v>
+        <v>19.7469</v>
       </c>
       <c r="F52">
-        <v>22.095</v>
+        <v>22.5369</v>
       </c>
       <c r="G52">
         <v>7.13</v>
@@ -5551,37 +5551,37 @@
         <v>2.068</v>
       </c>
       <c r="M52">
-        <v>5.210001</v>
+        <v>5.31420102</v>
       </c>
       <c r="N52">
-        <v>-3.142001</v>
+        <v>-3.24620102</v>
       </c>
       <c r="O52">
-        <v>-0.3142001</v>
+        <v>-0.324620102</v>
       </c>
       <c r="P52">
-        <v>-2.8278009</v>
+        <v>-2.921580918</v>
       </c>
       <c r="Q52">
-        <v>-2.8258009</v>
+        <v>-2.919580918</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1453145834463411</v>
+        <v>0.147345493312593</v>
       </c>
       <c r="T52">
-        <v>1.994636473374396</v>
+        <v>2.035343340177956</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03969289065395573</v>
+        <v>0.03891459868034876</v>
       </c>
       <c r="W52">
-        <v>0.2264404163837972</v>
+        <v>0.2266239376311738</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3969289065395573</v>
+        <v>0.3891459868034876</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1877774999150692</v>
+        <v>0.1896774999150692</v>
       </c>
       <c r="C53">
-        <v>-2.153537944585029</v>
+        <v>-2.770457582263976</v>
       </c>
       <c r="D53">
-        <v>13.25336205541497</v>
+        <v>13.07834241773602</v>
       </c>
       <c r="E53">
-        <v>19.7469</v>
+        <v>20.1888</v>
       </c>
       <c r="F53">
-        <v>22.5369</v>
+        <v>22.9788</v>
       </c>
       <c r="G53">
         <v>7.13</v>
@@ -5633,37 +5633,37 @@
         <v>2.068</v>
       </c>
       <c r="M53">
-        <v>5.31420102</v>
+        <v>5.41840104</v>
       </c>
       <c r="N53">
-        <v>-3.24620102</v>
+        <v>-3.35040104</v>
       </c>
       <c r="O53">
-        <v>-0.324620102</v>
+        <v>-0.335040104</v>
       </c>
       <c r="P53">
-        <v>-2.921580918</v>
+        <v>-3.015360936</v>
       </c>
       <c r="Q53">
-        <v>-2.919580918</v>
+        <v>-3.013360936</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.147345493312593</v>
+        <v>0.149461024423272</v>
       </c>
       <c r="T53">
-        <v>2.035343340177956</v>
+        <v>2.077746326431663</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03891459868034876</v>
+        <v>0.03816624101341898</v>
       </c>
       <c r="W53">
-        <v>0.2266239376311738</v>
+        <v>0.2268004003690358</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3891459868034876</v>
+        <v>0.3816624101341897</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1896774999150692</v>
+        <v>0.1915774999150692</v>
       </c>
       <c r="C54">
-        <v>-2.770457582263976</v>
+        <v>-3.382814961545247</v>
       </c>
       <c r="D54">
-        <v>13.07834241773602</v>
+        <v>12.90788503845475</v>
       </c>
       <c r="E54">
-        <v>20.1888</v>
+        <v>20.6307</v>
       </c>
       <c r="F54">
-        <v>22.9788</v>
+        <v>23.4207</v>
       </c>
       <c r="G54">
         <v>7.13</v>
@@ -5715,37 +5715,37 @@
         <v>2.068</v>
       </c>
       <c r="M54">
-        <v>5.41840104</v>
+        <v>5.52260106</v>
       </c>
       <c r="N54">
-        <v>-3.35040104</v>
+        <v>-3.45460106</v>
       </c>
       <c r="O54">
-        <v>-0.335040104</v>
+        <v>-0.345460106</v>
       </c>
       <c r="P54">
-        <v>-3.015360936</v>
+        <v>-3.109140954</v>
       </c>
       <c r="Q54">
-        <v>-3.013360936</v>
+        <v>-3.107140954000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.149461024423272</v>
+        <v>0.1516665781344054</v>
       </c>
       <c r="T54">
-        <v>2.077746326431663</v>
+        <v>2.121953695079145</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03816624101341898</v>
+        <v>0.0374461232584488</v>
       </c>
       <c r="W54">
-        <v>0.2268004003690358</v>
+        <v>0.2269702041356578</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3816624101341897</v>
+        <v>0.3744612325844879</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1915774999150692</v>
+        <v>0.1934774999150692</v>
       </c>
       <c r="C55">
-        <v>-3.382814961545247</v>
+        <v>-3.99078617474407</v>
       </c>
       <c r="D55">
-        <v>12.90788503845475</v>
+        <v>12.74181382525593</v>
       </c>
       <c r="E55">
-        <v>20.6307</v>
+        <v>21.0726</v>
       </c>
       <c r="F55">
-        <v>23.4207</v>
+        <v>23.8626</v>
       </c>
       <c r="G55">
         <v>7.13</v>
@@ -5797,37 +5797,37 @@
         <v>2.068</v>
       </c>
       <c r="M55">
-        <v>5.52260106</v>
+        <v>5.62680108</v>
       </c>
       <c r="N55">
-        <v>-3.45460106</v>
+        <v>-3.55880108</v>
       </c>
       <c r="O55">
-        <v>-0.345460106</v>
+        <v>-0.355880108</v>
       </c>
       <c r="P55">
-        <v>-3.109140954</v>
+        <v>-3.202920972</v>
       </c>
       <c r="Q55">
-        <v>-3.107140954000001</v>
+        <v>-3.200920972</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1516665781344054</v>
+        <v>0.1539680254851534</v>
       </c>
       <c r="T55">
-        <v>2.121953695079145</v>
+        <v>2.16808312323304</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0374461232584488</v>
+        <v>0.03675267653144049</v>
       </c>
       <c r="W55">
-        <v>0.2269702041356578</v>
+        <v>0.2271337188738863</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3744612325844879</v>
+        <v>0.3675267653144049</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1934774999150692</v>
+        <v>0.1953774999150692</v>
       </c>
       <c r="C56">
-        <v>-3.99078617474407</v>
+        <v>-4.594538366963704</v>
       </c>
       <c r="D56">
-        <v>12.74181382525593</v>
+        <v>12.5799616330363</v>
       </c>
       <c r="E56">
-        <v>21.0726</v>
+        <v>21.5145</v>
       </c>
       <c r="F56">
-        <v>23.8626</v>
+        <v>24.3045</v>
       </c>
       <c r="G56">
         <v>7.13</v>
@@ -5879,37 +5879,37 @@
         <v>2.068</v>
       </c>
       <c r="M56">
-        <v>5.62680108</v>
+        <v>5.7310011</v>
       </c>
       <c r="N56">
-        <v>-3.55880108</v>
+        <v>-3.6630011</v>
       </c>
       <c r="O56">
-        <v>-0.355880108</v>
+        <v>-0.3663001100000001</v>
       </c>
       <c r="P56">
-        <v>-3.202920972</v>
+        <v>-3.29670099</v>
       </c>
       <c r="Q56">
-        <v>-3.200920972</v>
+        <v>-3.29470099</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1539680254851534</v>
+        <v>0.1563717593848234</v>
       </c>
       <c r="T56">
-        <v>2.16808312323304</v>
+        <v>2.216262748193774</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03675267653144049</v>
+        <v>0.03608444604905067</v>
       </c>
       <c r="W56">
-        <v>0.2271337188738863</v>
+        <v>0.2272912876216339</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3675267653144049</v>
+        <v>0.3608444604905067</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1953774999150692</v>
+        <v>0.1972774999150692</v>
       </c>
       <c r="C57">
-        <v>-4.594538366963704</v>
+        <v>-5.194230297225097</v>
       </c>
       <c r="D57">
-        <v>12.5799616330363</v>
+        <v>12.4221697027749</v>
       </c>
       <c r="E57">
-        <v>21.5145</v>
+        <v>21.9564</v>
       </c>
       <c r="F57">
-        <v>24.3045</v>
+        <v>24.7464</v>
       </c>
       <c r="G57">
         <v>7.13</v>
@@ -5961,37 +5961,37 @@
         <v>2.068</v>
       </c>
       <c r="M57">
-        <v>5.7310011</v>
+        <v>5.835201120000001</v>
       </c>
       <c r="N57">
-        <v>-3.6630011</v>
+        <v>-3.767201120000001</v>
       </c>
       <c r="O57">
-        <v>-0.3663001100000001</v>
+        <v>-0.3767201120000001</v>
       </c>
       <c r="P57">
-        <v>-3.29670099</v>
+        <v>-3.390481008000001</v>
       </c>
       <c r="Q57">
-        <v>-3.29470099</v>
+        <v>-3.388481008000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1563717593848234</v>
+        <v>0.1588847539162967</v>
       </c>
       <c r="T57">
-        <v>2.216262748193774</v>
+        <v>2.266632356107269</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03608444604905067</v>
+        <v>0.0354400809410319</v>
       </c>
       <c r="W57">
-        <v>0.2272912876216339</v>
+        <v>0.2274432289141047</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3608444604905067</v>
+        <v>0.3544008094103189</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1972774999150692</v>
+        <v>0.1991774999150692</v>
       </c>
       <c r="C58">
-        <v>-5.194230297225097</v>
+        <v>-5.790012857889746</v>
       </c>
       <c r="D58">
-        <v>12.4221697027749</v>
+        <v>12.26828714211026</v>
       </c>
       <c r="E58">
-        <v>21.9564</v>
+        <v>22.3983</v>
       </c>
       <c r="F58">
-        <v>24.7464</v>
+        <v>25.1883</v>
       </c>
       <c r="G58">
         <v>7.13</v>
@@ -6043,37 +6043,37 @@
         <v>2.068</v>
       </c>
       <c r="M58">
-        <v>5.835201120000001</v>
+        <v>5.939401140000001</v>
       </c>
       <c r="N58">
-        <v>-3.767201120000001</v>
+        <v>-3.871401140000001</v>
       </c>
       <c r="O58">
-        <v>-0.3767201120000001</v>
+        <v>-0.3871401140000001</v>
       </c>
       <c r="P58">
-        <v>-3.390481008000001</v>
+        <v>-3.484261026000001</v>
       </c>
       <c r="Q58">
-        <v>-3.388481008000001</v>
+        <v>-3.482261026000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1588847539162967</v>
+        <v>0.1615146319143501</v>
       </c>
       <c r="T58">
-        <v>2.266632356107269</v>
+        <v>2.319344736481857</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0354400809410319</v>
+        <v>0.03481832513504888</v>
       </c>
       <c r="W58">
-        <v>0.2274432289141047</v>
+        <v>0.2275898389331555</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3544008094103189</v>
+        <v>0.3481832513504888</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1991774999150692</v>
+        <v>0.2010774999150692</v>
       </c>
       <c r="C59">
-        <v>-5.790012857889746</v>
+        <v>-6.382029555948115</v>
       </c>
       <c r="D59">
-        <v>12.26828714211026</v>
+        <v>12.11817044405189</v>
       </c>
       <c r="E59">
-        <v>22.3983</v>
+        <v>22.8402</v>
       </c>
       <c r="F59">
-        <v>25.1883</v>
+        <v>25.6302</v>
       </c>
       <c r="G59">
         <v>7.13</v>
@@ -6125,37 +6125,37 @@
         <v>2.068</v>
       </c>
       <c r="M59">
-        <v>5.939401140000001</v>
+        <v>6.043601160000001</v>
       </c>
       <c r="N59">
-        <v>-3.871401140000001</v>
+        <v>-3.975601160000001</v>
       </c>
       <c r="O59">
-        <v>-0.3871401140000001</v>
+        <v>-0.3975601160000001</v>
       </c>
       <c r="P59">
-        <v>-3.484261026000001</v>
+        <v>-3.578041044</v>
       </c>
       <c r="Q59">
-        <v>-3.482261026000001</v>
+        <v>-3.576041044000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1615146319143501</v>
+        <v>0.1642697421980251</v>
       </c>
       <c r="T59">
-        <v>2.319344736481857</v>
+        <v>2.374567230207615</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03481832513504888</v>
+        <v>0.03421800918444459</v>
       </c>
       <c r="W59">
-        <v>0.2275898389331555</v>
+        <v>0.227731393434308</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3481832513504888</v>
+        <v>0.3421800918444459</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2010774999150692</v>
+        <v>0.2029774999150692</v>
       </c>
       <c r="C60">
-        <v>-6.382029555948112</v>
+        <v>-6.970416959400517</v>
       </c>
       <c r="D60">
-        <v>12.11817044405189</v>
+        <v>11.97168304059948</v>
       </c>
       <c r="E60">
-        <v>22.8402</v>
+        <v>23.2821</v>
       </c>
       <c r="F60">
-        <v>25.6302</v>
+        <v>26.0721</v>
       </c>
       <c r="G60">
         <v>7.13</v>
@@ -6207,37 +6207,37 @@
         <v>2.068</v>
       </c>
       <c r="M60">
-        <v>6.04360116</v>
+        <v>6.14780118</v>
       </c>
       <c r="N60">
-        <v>-3.97560116</v>
+        <v>-4.07980118</v>
       </c>
       <c r="O60">
-        <v>-0.397560116</v>
+        <v>-0.4079801180000001</v>
       </c>
       <c r="P60">
-        <v>-3.578041044</v>
+        <v>-3.671821062</v>
       </c>
       <c r="Q60">
-        <v>-3.576041044</v>
+        <v>-3.669821062</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1642697421980251</v>
+        <v>0.167159248105294</v>
       </c>
       <c r="T60">
-        <v>2.374567230207615</v>
+        <v>2.432483504115117</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0342180091844446</v>
+        <v>0.03363804292708113</v>
       </c>
       <c r="W60">
-        <v>0.227731393434308</v>
+        <v>0.2278681494777943</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.342180091844446</v>
+        <v>0.3363804292708112</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2029774999150692</v>
+        <v>0.2048774999150692</v>
       </c>
       <c r="C61">
-        <v>-6.970416959400517</v>
+        <v>-7.555305111648842</v>
       </c>
       <c r="D61">
-        <v>11.97168304059948</v>
+        <v>11.82869488835116</v>
       </c>
       <c r="E61">
-        <v>23.2821</v>
+        <v>23.724</v>
       </c>
       <c r="F61">
-        <v>26.0721</v>
+        <v>26.514</v>
       </c>
       <c r="G61">
         <v>7.13</v>
@@ -6289,37 +6289,37 @@
         <v>2.068</v>
       </c>
       <c r="M61">
-        <v>6.14780118</v>
+        <v>6.2520012</v>
       </c>
       <c r="N61">
-        <v>-4.07980118</v>
+        <v>-4.184001200000001</v>
       </c>
       <c r="O61">
-        <v>-0.4079801180000001</v>
+        <v>-0.4184001200000001</v>
       </c>
       <c r="P61">
-        <v>-3.671821062</v>
+        <v>-3.765601080000001</v>
       </c>
       <c r="Q61">
-        <v>-3.669821062</v>
+        <v>-3.763601080000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.167159248105294</v>
+        <v>0.1701932293079264</v>
       </c>
       <c r="T61">
-        <v>2.432483504115117</v>
+        <v>2.493295591717995</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03363804292708113</v>
+        <v>0.03307740887829644</v>
       </c>
       <c r="W61">
-        <v>0.2278681494777943</v>
+        <v>0.2280003469864977</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3363804292708112</v>
+        <v>0.3307740887829643</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2048774999150692</v>
+        <v>0.2067774999150692</v>
       </c>
       <c r="C62">
-        <v>-7.555305111648842</v>
+        <v>-8.136817916542228</v>
       </c>
       <c r="D62">
-        <v>11.82869488835116</v>
+        <v>11.68908208345777</v>
       </c>
       <c r="E62">
-        <v>23.724</v>
+        <v>24.1659</v>
       </c>
       <c r="F62">
-        <v>26.514</v>
+        <v>26.9559</v>
       </c>
       <c r="G62">
         <v>7.13</v>
@@ -6371,37 +6371,37 @@
         <v>2.068</v>
       </c>
       <c r="M62">
-        <v>6.2520012</v>
+        <v>6.35620122</v>
       </c>
       <c r="N62">
-        <v>-4.184001200000001</v>
+        <v>-4.288201219999999</v>
       </c>
       <c r="O62">
-        <v>-0.4184001200000001</v>
+        <v>-0.428820122</v>
       </c>
       <c r="P62">
-        <v>-3.765601080000001</v>
+        <v>-3.859381098</v>
       </c>
       <c r="Q62">
-        <v>-3.763601080000001</v>
+        <v>-3.857381098</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1701932293079264</v>
+        <v>0.1733827992901809</v>
       </c>
       <c r="T62">
-        <v>2.493295591717995</v>
+        <v>2.557226247915893</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03307740887829644</v>
+        <v>0.0325351562737342</v>
       </c>
       <c r="W62">
-        <v>0.2280003469864977</v>
+        <v>0.2281282101506535</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3307740887829643</v>
+        <v>0.3253515627373421</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2067774999150692</v>
+        <v>0.2086774999150692</v>
       </c>
       <c r="C63">
-        <v>-8.136817916542228</v>
+        <v>-8.715073496472854</v>
       </c>
       <c r="D63">
-        <v>11.68908208345777</v>
+        <v>11.55272650352715</v>
       </c>
       <c r="E63">
-        <v>24.1659</v>
+        <v>24.6078</v>
       </c>
       <c r="F63">
-        <v>26.9559</v>
+        <v>27.3978</v>
       </c>
       <c r="G63">
         <v>7.13</v>
@@ -6453,37 +6453,37 @@
         <v>2.068</v>
       </c>
       <c r="M63">
-        <v>6.35620122</v>
+        <v>6.46040124</v>
       </c>
       <c r="N63">
-        <v>-4.288201219999999</v>
+        <v>-4.39240124</v>
       </c>
       <c r="O63">
-        <v>-0.428820122</v>
+        <v>-0.439240124</v>
       </c>
       <c r="P63">
-        <v>-3.859381098</v>
+        <v>-3.953161116</v>
       </c>
       <c r="Q63">
-        <v>-3.857381098</v>
+        <v>-3.951161116</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1733827992901809</v>
+        <v>0.1767402413767646</v>
       </c>
       <c r="T63">
-        <v>2.557226247915893</v>
+        <v>2.624521675492627</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0325351562737342</v>
+        <v>0.03201039568867398</v>
       </c>
       <c r="W63">
-        <v>0.2281282101506535</v>
+        <v>0.2282519486966107</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3253515627373421</v>
+        <v>0.3201039568867398</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2086774999150692</v>
+        <v>0.2105774999150692</v>
       </c>
       <c r="C64">
-        <v>-8.715073496472854</v>
+        <v>-9.2901845256972</v>
       </c>
       <c r="D64">
-        <v>11.55272650352715</v>
+        <v>11.4195154743028</v>
       </c>
       <c r="E64">
-        <v>24.6078</v>
+        <v>25.0497</v>
       </c>
       <c r="F64">
-        <v>27.3978</v>
+        <v>27.8397</v>
       </c>
       <c r="G64">
         <v>7.13</v>
@@ -6535,37 +6535,37 @@
         <v>2.068</v>
       </c>
       <c r="M64">
-        <v>6.46040124</v>
+        <v>6.56460126</v>
       </c>
       <c r="N64">
-        <v>-4.39240124</v>
+        <v>-4.49660126</v>
       </c>
       <c r="O64">
-        <v>-0.439240124</v>
+        <v>-0.449660126</v>
       </c>
       <c r="P64">
-        <v>-3.953161116</v>
+        <v>-4.046941134</v>
       </c>
       <c r="Q64">
-        <v>-3.951161116</v>
+        <v>-4.044941134</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1767402413767646</v>
+        <v>0.1802791668193799</v>
       </c>
       <c r="T64">
-        <v>2.624521675492627</v>
+        <v>2.695454693749184</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03201039568867398</v>
+        <v>0.03150229416980613</v>
       </c>
       <c r="W64">
-        <v>0.2282519486966107</v>
+        <v>0.2283717590347597</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3201039568867398</v>
+        <v>0.3150229416980613</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2105774999150692</v>
+        <v>0.2124774999150692</v>
       </c>
       <c r="C65">
-        <v>-9.2901845256972</v>
+        <v>-9.8622585408596</v>
       </c>
       <c r="D65">
-        <v>11.4195154743028</v>
+        <v>11.2893414591404</v>
       </c>
       <c r="E65">
-        <v>25.0497</v>
+        <v>25.4916</v>
       </c>
       <c r="F65">
-        <v>27.8397</v>
+        <v>28.2816</v>
       </c>
       <c r="G65">
         <v>7.13</v>
@@ -6617,37 +6617,37 @@
         <v>2.068</v>
       </c>
       <c r="M65">
-        <v>6.56460126</v>
+        <v>6.668801279999999</v>
       </c>
       <c r="N65">
-        <v>-4.49660126</v>
+        <v>-4.600801279999999</v>
       </c>
       <c r="O65">
-        <v>-0.449660126</v>
+        <v>-0.4600801279999999</v>
       </c>
       <c r="P65">
-        <v>-4.046941134</v>
+        <v>-4.140721151999999</v>
       </c>
       <c r="Q65">
-        <v>-4.044941134</v>
+        <v>-4.138721152</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1802791668193799</v>
+        <v>0.1840146992310293</v>
       </c>
       <c r="T65">
-        <v>2.695454693749184</v>
+        <v>2.770328435242217</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03150229416980613</v>
+        <v>0.03101007082340292</v>
       </c>
       <c r="W65">
-        <v>0.2283717590347597</v>
+        <v>0.2284878252998416</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3150229416980613</v>
+        <v>0.3101007082340292</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2124774999150692</v>
+        <v>0.2143774999150692</v>
       </c>
       <c r="C66">
-        <v>-9.8622585408596</v>
+        <v>-10.43139823051672</v>
       </c>
       <c r="D66">
-        <v>11.2893414591404</v>
+        <v>11.16210176948327</v>
       </c>
       <c r="E66">
-        <v>25.4916</v>
+        <v>25.9335</v>
       </c>
       <c r="F66">
-        <v>28.2816</v>
+        <v>28.7235</v>
       </c>
       <c r="G66">
         <v>7.13</v>
@@ -6699,37 +6699,37 @@
         <v>2.068</v>
       </c>
       <c r="M66">
-        <v>6.668801279999999</v>
+        <v>6.7730013</v>
       </c>
       <c r="N66">
-        <v>-4.600801279999999</v>
+        <v>-4.705001299999999</v>
       </c>
       <c r="O66">
-        <v>-0.4600801279999999</v>
+        <v>-0.47050013</v>
       </c>
       <c r="P66">
-        <v>-4.140721151999999</v>
+        <v>-4.23450117</v>
       </c>
       <c r="Q66">
-        <v>-4.138721152</v>
+        <v>-4.23250117</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1840146992310293</v>
+        <v>0.1879636906376301</v>
       </c>
       <c r="T66">
-        <v>2.770328435242217</v>
+        <v>2.849480676249138</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03101007082340292</v>
+        <v>0.03053299281073518</v>
       </c>
       <c r="W66">
-        <v>0.2284878252998416</v>
+        <v>0.2286003202952286</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3101007082340292</v>
+        <v>0.3053299281073518</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2143774999150692</v>
+        <v>0.2162774999150692</v>
       </c>
       <c r="C67">
-        <v>-10.43139823051672</v>
+        <v>-10.99770170530128</v>
       </c>
       <c r="D67">
-        <v>11.16210176948327</v>
+        <v>11.03769829469872</v>
       </c>
       <c r="E67">
-        <v>25.9335</v>
+        <v>26.3754</v>
       </c>
       <c r="F67">
-        <v>28.7235</v>
+        <v>29.1654</v>
       </c>
       <c r="G67">
         <v>7.13</v>
@@ -6781,37 +6781,37 @@
         <v>2.068</v>
       </c>
       <c r="M67">
-        <v>6.7730013</v>
+        <v>6.87720132</v>
       </c>
       <c r="N67">
-        <v>-4.705001299999999</v>
+        <v>-4.80920132</v>
       </c>
       <c r="O67">
-        <v>-0.47050013</v>
+        <v>-0.480920132</v>
       </c>
       <c r="P67">
-        <v>-4.23450117</v>
+        <v>-4.328281188</v>
       </c>
       <c r="Q67">
-        <v>-4.23250117</v>
+        <v>-4.326281188</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1879636906376301</v>
+        <v>0.192144975656384</v>
       </c>
       <c r="T67">
-        <v>2.849480676249138</v>
+        <v>2.933288931432936</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03053299281073518</v>
+        <v>0.03007037170754222</v>
       </c>
       <c r="W67">
-        <v>0.2286003202952286</v>
+        <v>0.2287094063513616</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3053299281073518</v>
+        <v>0.3007037170754222</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2162774999150692</v>
+        <v>0.2181774999150692</v>
       </c>
       <c r="C68">
-        <v>-10.99770170530128</v>
+        <v>-11.56126275021875</v>
       </c>
       <c r="D68">
-        <v>11.03769829469872</v>
+        <v>10.91603724978125</v>
       </c>
       <c r="E68">
-        <v>26.3754</v>
+        <v>26.8173</v>
       </c>
       <c r="F68">
-        <v>29.1654</v>
+        <v>29.6073</v>
       </c>
       <c r="G68">
         <v>7.13</v>
@@ -6863,37 +6863,37 @@
         <v>2.068</v>
       </c>
       <c r="M68">
-        <v>6.87720132</v>
+        <v>6.98140134</v>
       </c>
       <c r="N68">
-        <v>-4.80920132</v>
+        <v>-4.91340134</v>
       </c>
       <c r="O68">
-        <v>-0.480920132</v>
+        <v>-0.491340134</v>
       </c>
       <c r="P68">
-        <v>-4.328281188</v>
+        <v>-4.422061206</v>
       </c>
       <c r="Q68">
-        <v>-4.326281188</v>
+        <v>-4.420061206000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.192144975656384</v>
+        <v>0.1965796718883956</v>
       </c>
       <c r="T68">
-        <v>2.933288931432936</v>
+        <v>3.022176474809692</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03007037170754222</v>
+        <v>0.0296215601895192</v>
       </c>
       <c r="W68">
-        <v>0.2287094063513616</v>
+        <v>0.2288152361073114</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3007037170754222</v>
+        <v>0.2962156018951919</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2181774999150692</v>
+        <v>0.2200774999150692</v>
       </c>
       <c r="C69">
-        <v>-11.56126275021875</v>
+        <v>-12.12217106044061</v>
       </c>
       <c r="D69">
-        <v>10.91603724978125</v>
+        <v>10.79702893955938</v>
       </c>
       <c r="E69">
-        <v>26.8173</v>
+        <v>27.2592</v>
       </c>
       <c r="F69">
-        <v>29.6073</v>
+        <v>30.0492</v>
       </c>
       <c r="G69">
         <v>7.13</v>
@@ -6945,37 +6945,37 @@
         <v>2.068</v>
       </c>
       <c r="M69">
-        <v>6.98140134</v>
+        <v>7.08560136</v>
       </c>
       <c r="N69">
-        <v>-4.91340134</v>
+        <v>-5.01760136</v>
       </c>
       <c r="O69">
-        <v>-0.491340134</v>
+        <v>-0.501760136</v>
       </c>
       <c r="P69">
-        <v>-4.422061206</v>
+        <v>-4.515841224000001</v>
       </c>
       <c r="Q69">
-        <v>-4.420061206000001</v>
+        <v>-4.513841224000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1965796718883956</v>
+        <v>0.201291536634908</v>
       </c>
       <c r="T69">
-        <v>3.022176474809692</v>
+        <v>3.116619489647495</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0296215601895192</v>
+        <v>0.02918594901026157</v>
       </c>
       <c r="W69">
-        <v>0.2288152361073114</v>
+        <v>0.2289179532233803</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2962156018951919</v>
+        <v>0.2918594901026156</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2200774999150692</v>
+        <v>0.2219774999150692</v>
       </c>
       <c r="C70">
-        <v>-12.12217106044061</v>
+        <v>-12.68051246184007</v>
       </c>
       <c r="D70">
-        <v>10.79702893955938</v>
+        <v>10.68058753815993</v>
       </c>
       <c r="E70">
-        <v>27.2592</v>
+        <v>27.7011</v>
       </c>
       <c r="F70">
-        <v>30.0492</v>
+        <v>30.4911</v>
       </c>
       <c r="G70">
         <v>7.13</v>
@@ -7027,37 +7027,37 @@
         <v>2.068</v>
       </c>
       <c r="M70">
-        <v>7.08560136</v>
+        <v>7.18980138</v>
       </c>
       <c r="N70">
-        <v>-5.01760136</v>
+        <v>-5.121801380000001</v>
       </c>
       <c r="O70">
-        <v>-0.501760136</v>
+        <v>-0.5121801380000001</v>
       </c>
       <c r="P70">
-        <v>-4.515841224000001</v>
+        <v>-4.609621242000001</v>
       </c>
       <c r="Q70">
-        <v>-4.513841224000001</v>
+        <v>-4.607621242000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.201291536634908</v>
+        <v>0.2063073926553889</v>
       </c>
       <c r="T70">
-        <v>3.116619489647495</v>
+        <v>3.217155602216769</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02918594901026157</v>
+        <v>0.0287629642419969</v>
       </c>
       <c r="W70">
-        <v>0.2289179532233803</v>
+        <v>0.2290176930317371</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2918594901026156</v>
+        <v>0.287629642419969</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2219774999150692</v>
+        <v>0.2238774999150692</v>
       </c>
       <c r="C71">
-        <v>-12.68051246184007</v>
+        <v>-13.2363691174096</v>
       </c>
       <c r="D71">
-        <v>10.68058753815993</v>
+        <v>10.5666308825904</v>
       </c>
       <c r="E71">
-        <v>27.7011</v>
+        <v>28.143</v>
       </c>
       <c r="F71">
-        <v>30.4911</v>
+        <v>30.933</v>
       </c>
       <c r="G71">
         <v>7.13</v>
@@ -7109,37 +7109,37 @@
         <v>2.068</v>
       </c>
       <c r="M71">
-        <v>7.18980138</v>
+        <v>7.2940014</v>
       </c>
       <c r="N71">
-        <v>-5.121801380000001</v>
+        <v>-5.226001399999999</v>
       </c>
       <c r="O71">
-        <v>-0.5121801380000001</v>
+        <v>-0.52260014</v>
       </c>
       <c r="P71">
-        <v>-4.609621242000001</v>
+        <v>-4.70340126</v>
       </c>
       <c r="Q71">
-        <v>-4.607621242000001</v>
+        <v>-4.70140126</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2063073926553889</v>
+        <v>0.2116576390772352</v>
       </c>
       <c r="T71">
-        <v>3.217155602216769</v>
+        <v>3.324394122290661</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0287629642419969</v>
+        <v>0.02835206475282552</v>
       </c>
       <c r="W71">
-        <v>0.2290176930317371</v>
+        <v>0.2291145831312838</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.287629642419969</v>
+        <v>0.2835206475282552</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2238774999150692</v>
+        <v>0.2257774999150692</v>
       </c>
       <c r="C72">
-        <v>-13.2363691174096</v>
+        <v>-13.78981972060386</v>
       </c>
       <c r="D72">
-        <v>10.5666308825904</v>
+        <v>10.45508027939614</v>
       </c>
       <c r="E72">
-        <v>28.143</v>
+        <v>28.5849</v>
       </c>
       <c r="F72">
-        <v>30.933</v>
+        <v>31.3749</v>
       </c>
       <c r="G72">
         <v>7.13</v>
@@ -7191,37 +7191,37 @@
         <v>2.068</v>
       </c>
       <c r="M72">
-        <v>7.2940014</v>
+        <v>7.39820142</v>
       </c>
       <c r="N72">
-        <v>-5.226001399999999</v>
+        <v>-5.33020142</v>
       </c>
       <c r="O72">
-        <v>-0.52260014</v>
+        <v>-0.533020142</v>
       </c>
       <c r="P72">
-        <v>-4.70340126</v>
+        <v>-4.797181278</v>
       </c>
       <c r="Q72">
-        <v>-4.70140126</v>
+        <v>-4.795181278</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2116576390772352</v>
+        <v>0.217376868010933</v>
       </c>
       <c r="T72">
-        <v>3.324394122290661</v>
+        <v>3.43902840236965</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02835206475282552</v>
+        <v>0.02795273989715193</v>
       </c>
       <c r="W72">
-        <v>0.2291145831312838</v>
+        <v>0.2292087439322516</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2835206475282552</v>
+        <v>0.2795273989715192</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2257774999150692</v>
+        <v>0.2276774999150692</v>
       </c>
       <c r="C73">
-        <v>-13.78981972060386</v>
+        <v>-14.34093967656393</v>
       </c>
       <c r="D73">
-        <v>10.45508027939614</v>
+        <v>10.34586032343606</v>
       </c>
       <c r="E73">
-        <v>28.5849</v>
+        <v>29.0268</v>
       </c>
       <c r="F73">
-        <v>31.3749</v>
+        <v>31.8168</v>
       </c>
       <c r="G73">
         <v>7.13</v>
@@ -7273,37 +7273,37 @@
         <v>2.068</v>
       </c>
       <c r="M73">
-        <v>7.398201419999999</v>
+        <v>7.50240144</v>
       </c>
       <c r="N73">
-        <v>-5.33020142</v>
+        <v>-5.43440144</v>
       </c>
       <c r="O73">
-        <v>-0.533020142</v>
+        <v>-0.5434401440000001</v>
       </c>
       <c r="P73">
-        <v>-4.797181278</v>
+        <v>-4.890961296</v>
       </c>
       <c r="Q73">
-        <v>-4.795181278</v>
+        <v>-4.888961296000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2173768680109329</v>
+        <v>0.2235046132970376</v>
       </c>
       <c r="T73">
-        <v>3.439028402369649</v>
+        <v>3.561850845311421</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02795273989715193</v>
+        <v>0.02756450739858037</v>
       </c>
       <c r="W73">
-        <v>0.2292087439322516</v>
+        <v>0.2293002891554148</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2795273989715192</v>
+        <v>0.2756450739858036</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2276774999150692</v>
+        <v>0.2295774999150692</v>
       </c>
       <c r="C74">
-        <v>-14.34093967656393</v>
+        <v>-14.88980127209991</v>
       </c>
       <c r="D74">
-        <v>10.34586032343606</v>
+        <v>10.23889872790009</v>
       </c>
       <c r="E74">
-        <v>29.0268</v>
+        <v>29.4687</v>
       </c>
       <c r="F74">
-        <v>31.8168</v>
+        <v>32.2587</v>
       </c>
       <c r="G74">
         <v>7.13</v>
@@ -7355,37 +7355,37 @@
         <v>2.068</v>
       </c>
       <c r="M74">
-        <v>7.50240144</v>
+        <v>7.606601459999999</v>
       </c>
       <c r="N74">
-        <v>-5.43440144</v>
+        <v>-5.538601459999999</v>
       </c>
       <c r="O74">
-        <v>-0.5434401440000001</v>
+        <v>-0.5538601459999999</v>
       </c>
       <c r="P74">
-        <v>-4.890961296</v>
+        <v>-4.984741313999999</v>
       </c>
       <c r="Q74">
-        <v>-4.888961296000001</v>
+        <v>-4.982741313999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2235046132970376</v>
+        <v>0.2300862656413724</v>
       </c>
       <c r="T74">
-        <v>3.561850845311421</v>
+        <v>3.693771246989623</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02756450739858037</v>
+        <v>0.027186911406819</v>
       </c>
       <c r="W74">
-        <v>0.2293002891554148</v>
+        <v>0.2293893262902721</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2756450739858036</v>
+        <v>0.27186911406819</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2295774999150692</v>
+        <v>0.2314774999150692</v>
       </c>
       <c r="C75">
-        <v>-14.88980127209991</v>
+        <v>-15.43647383523712</v>
       </c>
       <c r="D75">
-        <v>10.23889872790009</v>
+        <v>10.13412616476288</v>
       </c>
       <c r="E75">
-        <v>29.4687</v>
+        <v>29.9106</v>
       </c>
       <c r="F75">
-        <v>32.2587</v>
+        <v>32.7006</v>
       </c>
       <c r="G75">
         <v>7.13</v>
@@ -7437,37 +7437,37 @@
         <v>2.068</v>
       </c>
       <c r="M75">
-        <v>7.606601459999999</v>
+        <v>7.710801480000001</v>
       </c>
       <c r="N75">
-        <v>-5.538601459999999</v>
+        <v>-5.642801480000001</v>
       </c>
       <c r="O75">
-        <v>-0.5538601459999999</v>
+        <v>-0.5642801480000001</v>
       </c>
       <c r="P75">
-        <v>-4.984741313999999</v>
+        <v>-5.078521332000001</v>
       </c>
       <c r="Q75">
-        <v>-4.982741313999999</v>
+        <v>-5.076521332000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2300862656413724</v>
+        <v>0.2371741989352713</v>
       </c>
       <c r="T75">
-        <v>3.693771246989623</v>
+        <v>3.835839371873839</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.027186911406819</v>
+        <v>0.02681952071213225</v>
       </c>
       <c r="W75">
-        <v>0.2293893262902721</v>
+        <v>0.2294759570160792</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.27186911406819</v>
+        <v>0.2681952071213224</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2314774999150692</v>
+        <v>0.2333774999150692</v>
       </c>
       <c r="C76">
-        <v>-15.43647383523712</v>
+        <v>-15.98102388506595</v>
       </c>
       <c r="D76">
-        <v>10.13412616476288</v>
+        <v>10.03147611493405</v>
       </c>
       <c r="E76">
-        <v>29.9106</v>
+        <v>30.3525</v>
       </c>
       <c r="F76">
-        <v>32.7006</v>
+        <v>33.1425</v>
       </c>
       <c r="G76">
         <v>7.13</v>
@@ -7519,37 +7519,37 @@
         <v>2.068</v>
       </c>
       <c r="M76">
-        <v>7.710801480000001</v>
+        <v>7.8150015</v>
       </c>
       <c r="N76">
-        <v>-5.642801480000001</v>
+        <v>-5.7470015</v>
       </c>
       <c r="O76">
-        <v>-0.5642801480000001</v>
+        <v>-0.57470015</v>
       </c>
       <c r="P76">
-        <v>-5.078521332000001</v>
+        <v>-5.17230135</v>
       </c>
       <c r="Q76">
-        <v>-5.076521332000001</v>
+        <v>-5.17030135</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2371741989352713</v>
+        <v>0.2448291668926822</v>
       </c>
       <c r="T76">
-        <v>3.835839371873839</v>
+        <v>3.989272946748793</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02681952071213225</v>
+        <v>0.02646192710263715</v>
       </c>
       <c r="W76">
-        <v>0.2294759570160792</v>
+        <v>0.2295602775891982</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2681952071213224</v>
+        <v>0.2646192710263716</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2333774999150692</v>
+        <v>0.2352774999150692</v>
       </c>
       <c r="C77">
-        <v>-15.98102388506595</v>
+        <v>-16.52351527257591</v>
       </c>
       <c r="D77">
-        <v>10.03147611493405</v>
+        <v>9.93088472742409</v>
       </c>
       <c r="E77">
-        <v>30.3525</v>
+        <v>30.7944</v>
       </c>
       <c r="F77">
-        <v>33.1425</v>
+        <v>33.5844</v>
       </c>
       <c r="G77">
         <v>7.13</v>
@@ -7601,37 +7601,37 @@
         <v>2.068</v>
       </c>
       <c r="M77">
-        <v>7.8150015</v>
+        <v>7.919201519999999</v>
       </c>
       <c r="N77">
-        <v>-5.7470015</v>
+        <v>-5.851201519999998</v>
       </c>
       <c r="O77">
-        <v>-0.57470015</v>
+        <v>-0.5851201519999999</v>
       </c>
       <c r="P77">
-        <v>-5.17230135</v>
+        <v>-5.266081367999998</v>
       </c>
       <c r="Q77">
-        <v>-5.17030135</v>
+        <v>-5.264081367999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2448291668926822</v>
+        <v>0.253122048846544</v>
       </c>
       <c r="T77">
-        <v>3.989272946748793</v>
+        <v>4.155492652863327</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02646192710263715</v>
+        <v>0.02611374385128667</v>
       </c>
       <c r="W77">
-        <v>0.2295602775891982</v>
+        <v>0.2296423791998666</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2646192710263716</v>
+        <v>0.2611374385128667</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2352774999150692</v>
+        <v>0.2371774999150692</v>
       </c>
       <c r="C78">
-        <v>-16.52351527257591</v>
+        <v>-17.06400931310042</v>
       </c>
       <c r="D78">
-        <v>9.93088472742409</v>
+        <v>9.832290686899583</v>
       </c>
       <c r="E78">
-        <v>30.7944</v>
+        <v>31.2363</v>
       </c>
       <c r="F78">
-        <v>33.5844</v>
+        <v>34.0263</v>
       </c>
       <c r="G78">
         <v>7.13</v>
@@ -7683,37 +7683,37 @@
         <v>2.068</v>
       </c>
       <c r="M78">
-        <v>7.919201519999999</v>
+        <v>8.02340154</v>
       </c>
       <c r="N78">
-        <v>-5.851201519999998</v>
+        <v>-5.95540154</v>
       </c>
       <c r="O78">
-        <v>-0.5851201519999999</v>
+        <v>-0.595540154</v>
       </c>
       <c r="P78">
-        <v>-5.266081367999998</v>
+        <v>-5.359861386</v>
       </c>
       <c r="Q78">
-        <v>-5.264081367999998</v>
+        <v>-5.357861386000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.253122048846544</v>
+        <v>0.2621360509703067</v>
       </c>
       <c r="T78">
-        <v>4.155492652863327</v>
+        <v>4.336166246466079</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02611374385128667</v>
+        <v>0.02577460432075047</v>
       </c>
       <c r="W78">
-        <v>0.2296423791998666</v>
+        <v>0.229722348301167</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2611374385128667</v>
+        <v>0.2577460432075047</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2371774999150692</v>
+        <v>0.2390774999150692</v>
       </c>
       <c r="C79">
-        <v>-17.06400931310042</v>
+        <v>-17.60256491094971</v>
       </c>
       <c r="D79">
-        <v>9.832290686899583</v>
+        <v>9.735635089050282</v>
       </c>
       <c r="E79">
-        <v>31.2363</v>
+        <v>31.6782</v>
       </c>
       <c r="F79">
-        <v>34.0263</v>
+        <v>34.4682</v>
       </c>
       <c r="G79">
         <v>7.13</v>
@@ -7765,37 +7765,37 @@
         <v>2.068</v>
       </c>
       <c r="M79">
-        <v>8.02340154</v>
+        <v>8.127601559999999</v>
       </c>
       <c r="N79">
-        <v>-5.95540154</v>
+        <v>-6.059601559999999</v>
       </c>
       <c r="O79">
-        <v>-0.595540154</v>
+        <v>-0.605960156</v>
       </c>
       <c r="P79">
-        <v>-5.359861386</v>
+        <v>-5.453641403999999</v>
       </c>
       <c r="Q79">
-        <v>-5.357861386000001</v>
+        <v>-5.451641403999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2621360509703067</v>
+        <v>0.2719695078325934</v>
       </c>
       <c r="T79">
-        <v>4.336166246466079</v>
+        <v>4.533264712214537</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02577460432075047</v>
+        <v>0.02544416067561266</v>
       </c>
       <c r="W79">
-        <v>0.229722348301167</v>
+        <v>0.2298002669126906</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2577460432075047</v>
+        <v>0.2544416067561265</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2390774999150692</v>
+        <v>0.2409774999150692</v>
       </c>
       <c r="C80">
-        <v>-17.60256491094971</v>
+        <v>-18.13923867676414</v>
       </c>
       <c r="D80">
-        <v>9.735635089050282</v>
+        <v>9.640861323235859</v>
       </c>
       <c r="E80">
-        <v>31.6782</v>
+        <v>32.1201</v>
       </c>
       <c r="F80">
-        <v>34.4682</v>
+        <v>34.9101</v>
       </c>
       <c r="G80">
         <v>7.13</v>
@@ -7847,37 +7847,37 @@
         <v>2.068</v>
       </c>
       <c r="M80">
-        <v>8.127601559999999</v>
+        <v>8.231801580000001</v>
       </c>
       <c r="N80">
-        <v>-6.059601559999999</v>
+        <v>-6.163801580000001</v>
       </c>
       <c r="O80">
-        <v>-0.605960156</v>
+        <v>-0.6163801580000001</v>
       </c>
       <c r="P80">
-        <v>-5.453641403999999</v>
+        <v>-5.547421422000001</v>
       </c>
       <c r="Q80">
-        <v>-5.451641403999999</v>
+        <v>-5.545421422000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2719695078325934</v>
+        <v>0.2827394843960502</v>
       </c>
       <c r="T80">
-        <v>4.533264712214537</v>
+        <v>4.74913446041523</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02544416067561266</v>
+        <v>0.02512208269237704</v>
       </c>
       <c r="W80">
-        <v>0.2298002669126906</v>
+        <v>0.2298762129011375</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2544416067561265</v>
+        <v>0.2512208269237703</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2409774999150692</v>
+        <v>0.2428774999150692</v>
       </c>
       <c r="C81">
-        <v>-18.13923867676414</v>
+        <v>-18.67408503807907</v>
       </c>
       <c r="D81">
-        <v>9.640861323235859</v>
+        <v>9.547914961920931</v>
       </c>
       <c r="E81">
-        <v>32.1201</v>
+        <v>32.562</v>
       </c>
       <c r="F81">
-        <v>34.9101</v>
+        <v>35.352</v>
       </c>
       <c r="G81">
         <v>7.13</v>
@@ -7929,37 +7929,37 @@
         <v>2.068</v>
       </c>
       <c r="M81">
-        <v>8.231801580000001</v>
+        <v>8.336001599999999</v>
       </c>
       <c r="N81">
-        <v>-6.163801580000001</v>
+        <v>-6.2680016</v>
       </c>
       <c r="O81">
-        <v>-0.6163801580000001</v>
+        <v>-0.6268001600000001</v>
       </c>
       <c r="P81">
-        <v>-5.547421422000001</v>
+        <v>-5.64120144</v>
       </c>
       <c r="Q81">
-        <v>-5.545421422000001</v>
+        <v>-5.63920144</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2827394843960502</v>
+        <v>0.2945864586158528</v>
       </c>
       <c r="T81">
-        <v>4.74913446041523</v>
+        <v>4.986591183435992</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02512208269237704</v>
+        <v>0.02480805665872234</v>
       </c>
       <c r="W81">
-        <v>0.2298762129011375</v>
+        <v>0.2299502602398733</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2512208269237703</v>
+        <v>0.2480805665872233</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2428774999150692</v>
+        <v>0.2447774999150692</v>
       </c>
       <c r="C82">
-        <v>-18.67408503807907</v>
+        <v>-19.20715634355528</v>
       </c>
       <c r="D82">
-        <v>9.547914961920931</v>
+        <v>9.456743656444718</v>
       </c>
       <c r="E82">
-        <v>32.562</v>
+        <v>33.0039</v>
       </c>
       <c r="F82">
-        <v>35.352</v>
+        <v>35.7939</v>
       </c>
       <c r="G82">
         <v>7.13</v>
@@ -8011,37 +8011,37 @@
         <v>2.068</v>
       </c>
       <c r="M82">
-        <v>8.336001599999999</v>
+        <v>8.44020162</v>
       </c>
       <c r="N82">
-        <v>-6.2680016</v>
+        <v>-6.37220162</v>
       </c>
       <c r="O82">
-        <v>-0.6268001600000001</v>
+        <v>-0.6372201620000001</v>
       </c>
       <c r="P82">
-        <v>-5.64120144</v>
+        <v>-5.734981458</v>
       </c>
       <c r="Q82">
-        <v>-5.63920144</v>
+        <v>-5.732981458</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2945864586158528</v>
+        <v>0.3076804827535293</v>
       </c>
       <c r="T82">
-        <v>4.986591183435992</v>
+        <v>5.249043350985255</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02480805665872234</v>
+        <v>0.02450178435429366</v>
       </c>
       <c r="W82">
-        <v>0.2299502602398733</v>
+        <v>0.2300224792492576</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2480805665872233</v>
+        <v>0.2450178435429365</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2447774999150692</v>
+        <v>0.2466774999150692</v>
       </c>
       <c r="C83">
-        <v>-19.20715634355528</v>
+        <v>-19.73850296129416</v>
       </c>
       <c r="D83">
-        <v>9.456743656444718</v>
+        <v>9.367297038705843</v>
       </c>
       <c r="E83">
-        <v>33.0039</v>
+        <v>33.4458</v>
       </c>
       <c r="F83">
-        <v>35.7939</v>
+        <v>36.2358</v>
       </c>
       <c r="G83">
         <v>7.13</v>
@@ -8093,37 +8093,37 @@
         <v>2.068</v>
       </c>
       <c r="M83">
-        <v>8.44020162</v>
+        <v>8.54440164</v>
       </c>
       <c r="N83">
-        <v>-6.37220162</v>
+        <v>-6.476401640000001</v>
       </c>
       <c r="O83">
-        <v>-0.6372201620000001</v>
+        <v>-0.6476401640000001</v>
       </c>
       <c r="P83">
-        <v>-5.734981458</v>
+        <v>-5.828761476</v>
       </c>
       <c r="Q83">
-        <v>-5.732981458</v>
+        <v>-5.826761476000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3076804827535293</v>
+        <v>0.3222293984620587</v>
       </c>
       <c r="T83">
-        <v>5.249043350985255</v>
+        <v>5.540656870484436</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02450178435429366</v>
+        <v>0.02420298210607057</v>
       </c>
       <c r="W83">
-        <v>0.2300224792492576</v>
+        <v>0.2300929368193886</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2450178435429365</v>
+        <v>0.2420298210607056</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2466774999150692</v>
+        <v>0.2485774999150692</v>
       </c>
       <c r="C84">
-        <v>-19.73850296129416</v>
+        <v>-20.26817337162566</v>
       </c>
       <c r="D84">
-        <v>9.367297038705843</v>
+        <v>9.279526628374342</v>
       </c>
       <c r="E84">
-        <v>33.4458</v>
+        <v>33.8877</v>
       </c>
       <c r="F84">
-        <v>36.2358</v>
+        <v>36.6777</v>
       </c>
       <c r="G84">
         <v>7.13</v>
@@ -8175,37 +8175,37 @@
         <v>2.068</v>
       </c>
       <c r="M84">
-        <v>8.54440164</v>
+        <v>8.648601660000001</v>
       </c>
       <c r="N84">
-        <v>-6.476401640000001</v>
+        <v>-6.580601660000001</v>
       </c>
       <c r="O84">
-        <v>-0.6476401640000001</v>
+        <v>-0.6580601660000002</v>
       </c>
       <c r="P84">
-        <v>-5.828761476</v>
+        <v>-5.922541494000001</v>
       </c>
       <c r="Q84">
-        <v>-5.826761476000001</v>
+        <v>-5.920541494000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3222293984620587</v>
+        <v>0.338489951312768</v>
       </c>
       <c r="T84">
-        <v>5.540656870484436</v>
+        <v>5.866577862865874</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02420298210607057</v>
+        <v>0.02391137991202152</v>
       </c>
       <c r="W84">
-        <v>0.2300929368193886</v>
+        <v>0.2301616966167453</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2420298210607056</v>
+        <v>0.2391137991202151</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2485774999150692</v>
+        <v>0.2504774999150692</v>
       </c>
       <c r="C85">
-        <v>-20.26817337162566</v>
+        <v>-20.79621425472823</v>
       </c>
       <c r="D85">
-        <v>9.279526628374342</v>
+        <v>9.193385745271767</v>
       </c>
       <c r="E85">
-        <v>33.8877</v>
+        <v>34.3296</v>
       </c>
       <c r="F85">
-        <v>36.6777</v>
+        <v>37.1196</v>
       </c>
       <c r="G85">
         <v>7.13</v>
@@ -8257,37 +8257,37 @@
         <v>2.068</v>
       </c>
       <c r="M85">
-        <v>8.648601660000001</v>
+        <v>8.752801679999999</v>
       </c>
       <c r="N85">
-        <v>-6.580601660000001</v>
+        <v>-6.68480168</v>
       </c>
       <c r="O85">
-        <v>-0.6580601660000002</v>
+        <v>-0.668480168</v>
       </c>
       <c r="P85">
-        <v>-5.922541494000001</v>
+        <v>-6.016321511999999</v>
       </c>
       <c r="Q85">
-        <v>-5.920541494000001</v>
+        <v>-6.014321512</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.338489951312768</v>
+        <v>0.3567830732698161</v>
       </c>
       <c r="T85">
-        <v>5.866577862865874</v>
+        <v>6.233238979294993</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02391137991202152</v>
+        <v>0.0236267206273546</v>
       </c>
       <c r="W85">
-        <v>0.2301616966167453</v>
+        <v>0.2302288192760698</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2391137991202151</v>
+        <v>0.236267206273546</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2504774999150692</v>
+        <v>0.2523774999150692</v>
       </c>
       <c r="C86">
-        <v>-20.79621425472823</v>
+        <v>-21.32267057341346</v>
       </c>
       <c r="D86">
-        <v>9.193385745271767</v>
+        <v>9.108829426586537</v>
       </c>
       <c r="E86">
-        <v>34.3296</v>
+        <v>34.7715</v>
       </c>
       <c r="F86">
-        <v>37.1196</v>
+        <v>37.5615</v>
       </c>
       <c r="G86">
         <v>7.13</v>
@@ -8339,37 +8339,37 @@
         <v>2.068</v>
       </c>
       <c r="M86">
-        <v>8.752801679999999</v>
+        <v>8.8570017</v>
       </c>
       <c r="N86">
-        <v>-6.68480168</v>
+        <v>-6.7890017</v>
       </c>
       <c r="O86">
-        <v>-0.668480168</v>
+        <v>-0.67890017</v>
       </c>
       <c r="P86">
-        <v>-6.016321511999999</v>
+        <v>-6.11010153</v>
       </c>
       <c r="Q86">
-        <v>-6.014321512</v>
+        <v>-6.10810153</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3567830732698159</v>
+        <v>0.3775152781544703</v>
       </c>
       <c r="T86">
-        <v>6.233238979294988</v>
+        <v>6.648788244581321</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0236267206273546</v>
+        <v>0.02334875920820926</v>
       </c>
       <c r="W86">
-        <v>0.2302288192760698</v>
+        <v>0.2302943625787043</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.236267206273546</v>
+        <v>0.2334875920820925</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2523774999150692</v>
+        <v>0.2542774999150692</v>
       </c>
       <c r="C87">
-        <v>-21.32267057341346</v>
+        <v>-21.84758565138382</v>
       </c>
       <c r="D87">
-        <v>9.108829426586537</v>
+        <v>9.02581434861618</v>
       </c>
       <c r="E87">
-        <v>34.7715</v>
+        <v>35.2134</v>
       </c>
       <c r="F87">
-        <v>37.5615</v>
+        <v>38.0034</v>
       </c>
       <c r="G87">
         <v>7.13</v>
@@ -8421,37 +8421,37 @@
         <v>2.068</v>
       </c>
       <c r="M87">
-        <v>8.8570017</v>
+        <v>8.96120172</v>
       </c>
       <c r="N87">
-        <v>-6.7890017</v>
+        <v>-6.89320172</v>
       </c>
       <c r="O87">
-        <v>-0.67890017</v>
+        <v>-0.6893201720000001</v>
       </c>
       <c r="P87">
-        <v>-6.11010153</v>
+        <v>-6.203881548</v>
       </c>
       <c r="Q87">
-        <v>-6.10810153</v>
+        <v>-6.201881548</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3775152781544703</v>
+        <v>0.4012092265940753</v>
       </c>
       <c r="T87">
-        <v>6.648788244581321</v>
+        <v>7.123701690622844</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02334875920820926</v>
+        <v>0.0230772620081138</v>
       </c>
       <c r="W87">
-        <v>0.2302943625787043</v>
+        <v>0.2303583816184868</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2334875920820925</v>
+        <v>0.2307726200811379</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2542774999150692</v>
+        <v>0.2561774999150692</v>
       </c>
       <c r="C88">
-        <v>-21.84758565138382</v>
+        <v>-22.37100124724979</v>
       </c>
       <c r="D88">
-        <v>9.02581434861618</v>
+        <v>8.944298752750207</v>
       </c>
       <c r="E88">
-        <v>35.2134</v>
+        <v>35.6553</v>
       </c>
       <c r="F88">
-        <v>38.0034</v>
+        <v>38.4453</v>
       </c>
       <c r="G88">
         <v>7.13</v>
@@ -8503,37 +8503,37 @@
         <v>2.068</v>
       </c>
       <c r="M88">
-        <v>8.96120172</v>
+        <v>9.065401739999999</v>
       </c>
       <c r="N88">
-        <v>-6.89320172</v>
+        <v>-6.997401739999999</v>
       </c>
       <c r="O88">
-        <v>-0.6893201720000001</v>
+        <v>-0.699740174</v>
       </c>
       <c r="P88">
-        <v>-6.203881548</v>
+        <v>-6.297661565999999</v>
       </c>
       <c r="Q88">
-        <v>-6.201881548</v>
+        <v>-6.295661565999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4012092265940753</v>
+        <v>0.4285483978705426</v>
       </c>
       <c r="T88">
-        <v>7.123701690622844</v>
+        <v>7.671678743747678</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0230772620081138</v>
+        <v>0.02281200612296307</v>
       </c>
       <c r="W88">
-        <v>0.2303583816184868</v>
+        <v>0.2304209289562053</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2307726200811379</v>
+        <v>0.2281200612296306</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2561774999150692</v>
+        <v>0.2580774999150692</v>
       </c>
       <c r="C89">
-        <v>-22.37100124724979</v>
+        <v>-22.89295762457204</v>
       </c>
       <c r="D89">
-        <v>8.944298752750207</v>
+        <v>8.864242375427954</v>
       </c>
       <c r="E89">
-        <v>35.6553</v>
+        <v>36.0972</v>
       </c>
       <c r="F89">
-        <v>38.4453</v>
+        <v>38.8872</v>
       </c>
       <c r="G89">
         <v>7.13</v>
@@ -8585,37 +8585,37 @@
         <v>2.068</v>
       </c>
       <c r="M89">
-        <v>9.065401739999999</v>
+        <v>9.169601760000001</v>
       </c>
       <c r="N89">
-        <v>-6.997401739999999</v>
+        <v>-7.101601760000001</v>
       </c>
       <c r="O89">
-        <v>-0.699740174</v>
+        <v>-0.7101601760000001</v>
       </c>
       <c r="P89">
-        <v>-6.297661565999999</v>
+        <v>-6.391441584000001</v>
       </c>
       <c r="Q89">
-        <v>-6.295661565999999</v>
+        <v>-6.389441584000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4285483978705426</v>
+        <v>0.460444097693088</v>
       </c>
       <c r="T89">
-        <v>7.671678743747678</v>
+        <v>8.310985305726653</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02281200612296307</v>
+        <v>0.02255277878065666</v>
       </c>
       <c r="W89">
-        <v>0.2304209289562053</v>
+        <v>0.2304820547635212</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2281200612296306</v>
+        <v>0.2255277878065666</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2580774999150692</v>
+        <v>0.2599774999150692</v>
       </c>
       <c r="C90">
-        <v>-22.89295762457204</v>
+        <v>-23.41349361817544</v>
       </c>
       <c r="D90">
-        <v>8.864242375427954</v>
+        <v>8.785606381824557</v>
       </c>
       <c r="E90">
-        <v>36.0972</v>
+        <v>36.5391</v>
       </c>
       <c r="F90">
-        <v>38.8872</v>
+        <v>39.3291</v>
       </c>
       <c r="G90">
         <v>7.13</v>
@@ -8667,37 +8667,37 @@
         <v>2.068</v>
       </c>
       <c r="M90">
-        <v>9.169601760000001</v>
+        <v>9.273801779999999</v>
       </c>
       <c r="N90">
-        <v>-7.101601760000001</v>
+        <v>-7.20580178</v>
       </c>
       <c r="O90">
-        <v>-0.7101601760000001</v>
+        <v>-0.7205801780000001</v>
       </c>
       <c r="P90">
-        <v>-6.391441584000001</v>
+        <v>-6.485221601999999</v>
       </c>
       <c r="Q90">
-        <v>-6.389441584000001</v>
+        <v>-6.483221602</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.460444097693088</v>
+        <v>0.4981390156651868</v>
       </c>
       <c r="T90">
-        <v>8.310985305726653</v>
+        <v>9.066529424429074</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02255277878065666</v>
+        <v>0.02229937677188525</v>
       </c>
       <c r="W90">
-        <v>0.2304820547635212</v>
+        <v>0.2305418069571895</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2255277878065666</v>
+        <v>0.2229937677188524</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2599774999150692</v>
+        <v>0.2618774999150691</v>
       </c>
       <c r="C91">
-        <v>-23.41349361817544</v>
+        <v>-23.93264669696443</v>
       </c>
       <c r="D91">
-        <v>8.785606381824557</v>
+        <v>8.708353303035569</v>
       </c>
       <c r="E91">
-        <v>36.5391</v>
+        <v>36.981</v>
       </c>
       <c r="F91">
-        <v>39.3291</v>
+        <v>39.771</v>
       </c>
       <c r="G91">
         <v>7.13</v>
@@ -8749,37 +8749,37 @@
         <v>2.068</v>
       </c>
       <c r="M91">
-        <v>9.273801779999999</v>
+        <v>9.3780018</v>
       </c>
       <c r="N91">
-        <v>-7.20580178</v>
+        <v>-7.3100018</v>
       </c>
       <c r="O91">
-        <v>-0.7205801780000001</v>
+        <v>-0.7310001800000001</v>
       </c>
       <c r="P91">
-        <v>-6.485221601999999</v>
+        <v>-6.57900162</v>
       </c>
       <c r="Q91">
-        <v>-6.483221602</v>
+        <v>-6.57700162</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4981390156651868</v>
+        <v>0.5433729172317056</v>
       </c>
       <c r="T91">
-        <v>9.066529424429074</v>
+        <v>9.973182366871985</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02229937677188525</v>
+        <v>0.0220516059188643</v>
       </c>
       <c r="W91">
-        <v>0.2305418069571895</v>
+        <v>0.2306002313243318</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2229937677188524</v>
+        <v>0.2205160591886429</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2618774999150691</v>
+        <v>0.2637774999150692</v>
       </c>
       <c r="C92">
-        <v>-23.93264669696443</v>
+        <v>-24.45045302345324</v>
       </c>
       <c r="D92">
-        <v>8.708353303035569</v>
+        <v>8.63244697654676</v>
       </c>
       <c r="E92">
-        <v>36.981</v>
+        <v>37.4229</v>
       </c>
       <c r="F92">
-        <v>39.771</v>
+        <v>40.2129</v>
       </c>
       <c r="G92">
         <v>7.13</v>
@@ -8831,37 +8831,37 @@
         <v>2.068</v>
       </c>
       <c r="M92">
-        <v>9.3780018</v>
+        <v>9.48220182</v>
       </c>
       <c r="N92">
-        <v>-7.3100018</v>
+        <v>-7.414201820000001</v>
       </c>
       <c r="O92">
-        <v>-0.7310001800000001</v>
+        <v>-0.7414201820000001</v>
       </c>
       <c r="P92">
-        <v>-6.57900162</v>
+        <v>-6.672781638</v>
       </c>
       <c r="Q92">
-        <v>-6.57700162</v>
+        <v>-6.670781638</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5433729172317056</v>
+        <v>0.5986587969241173</v>
       </c>
       <c r="T92">
-        <v>9.973182366871985</v>
+        <v>11.08131374096887</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0220516059188643</v>
+        <v>0.02180928057909656</v>
       </c>
       <c r="W92">
-        <v>0.2306002313243318</v>
+        <v>0.230657371639449</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2205160591886429</v>
+        <v>0.2180928057909655</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2637774999150692</v>
+        <v>0.2656774999150692</v>
       </c>
       <c r="C93">
-        <v>-24.45045302345324</v>
+        <v>-24.96694751020961</v>
       </c>
       <c r="D93">
-        <v>8.63244697654676</v>
+        <v>8.557852489790386</v>
       </c>
       <c r="E93">
-        <v>37.4229</v>
+        <v>37.8648</v>
       </c>
       <c r="F93">
-        <v>40.2129</v>
+        <v>40.6548</v>
       </c>
       <c r="G93">
         <v>7.13</v>
@@ -8913,37 +8913,37 @@
         <v>2.068</v>
       </c>
       <c r="M93">
-        <v>9.48220182</v>
+        <v>9.586401840000001</v>
       </c>
       <c r="N93">
-        <v>-7.414201820000001</v>
+        <v>-7.518401840000001</v>
       </c>
       <c r="O93">
-        <v>-0.7414201820000001</v>
+        <v>-0.7518401840000002</v>
       </c>
       <c r="P93">
-        <v>-6.672781638</v>
+        <v>-6.766561656</v>
       </c>
       <c r="Q93">
-        <v>-6.670781638</v>
+        <v>-6.764561656000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5986587969241173</v>
+        <v>0.6677661465396322</v>
       </c>
       <c r="T93">
-        <v>11.08131374096887</v>
+        <v>12.46647795858999</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02180928057909656</v>
+        <v>0.02157222318149768</v>
       </c>
       <c r="W93">
-        <v>0.230657371639449</v>
+        <v>0.2307132697738029</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2180928057909655</v>
+        <v>0.2157222318149767</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2656774999150692</v>
+        <v>0.2675774999150692</v>
       </c>
       <c r="C94">
-        <v>-24.96694751020961</v>
+        <v>-25.48216387339717</v>
       </c>
       <c r="D94">
-        <v>8.557852489790386</v>
+        <v>8.48453612660283</v>
       </c>
       <c r="E94">
-        <v>37.8648</v>
+        <v>38.3067</v>
       </c>
       <c r="F94">
-        <v>40.6548</v>
+        <v>41.0967</v>
       </c>
       <c r="G94">
         <v>7.13</v>
@@ -8995,37 +8995,37 @@
         <v>2.068</v>
       </c>
       <c r="M94">
-        <v>9.586401840000001</v>
+        <v>9.690601859999999</v>
       </c>
       <c r="N94">
-        <v>-7.518401840000001</v>
+        <v>-7.62260186</v>
       </c>
       <c r="O94">
-        <v>-0.7518401840000002</v>
+        <v>-0.762260186</v>
       </c>
       <c r="P94">
-        <v>-6.766561656</v>
+        <v>-6.860341674</v>
       </c>
       <c r="Q94">
-        <v>-6.764561656000001</v>
+        <v>-6.858341674</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6677661465396322</v>
+        <v>0.7566184531881511</v>
       </c>
       <c r="T94">
-        <v>12.46647795858999</v>
+        <v>14.2474033812457</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02157222318149768</v>
+        <v>0.02134026379244932</v>
       </c>
       <c r="W94">
-        <v>0.2307132697738029</v>
+        <v>0.2307679657977404</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2157222318149767</v>
+        <v>0.2134026379244931</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2675774999150692</v>
+        <v>0.2694774999150692</v>
       </c>
       <c r="C95">
-        <v>-25.48216387339717</v>
+        <v>-25.99613468358893</v>
       </c>
       <c r="D95">
-        <v>8.48453612660283</v>
+        <v>8.412465316411074</v>
       </c>
       <c r="E95">
-        <v>38.3067</v>
+        <v>38.7486</v>
       </c>
       <c r="F95">
-        <v>41.0967</v>
+        <v>41.5386</v>
       </c>
       <c r="G95">
         <v>7.13</v>
@@ -9077,37 +9077,37 @@
         <v>2.068</v>
       </c>
       <c r="M95">
-        <v>9.690601859999999</v>
+        <v>9.794801880000001</v>
       </c>
       <c r="N95">
-        <v>-7.62260186</v>
+        <v>-7.726801880000002</v>
       </c>
       <c r="O95">
-        <v>-0.762260186</v>
+        <v>-0.7726801880000003</v>
       </c>
       <c r="P95">
-        <v>-6.860341674</v>
+        <v>-6.954121692000001</v>
       </c>
       <c r="Q95">
-        <v>-6.858341674</v>
+        <v>-6.952121692000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7566184531881511</v>
+        <v>0.8750881953861765</v>
       </c>
       <c r="T95">
-        <v>14.2474033812457</v>
+        <v>16.62197061145332</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02134026379244932</v>
+        <v>0.02111323970955092</v>
       </c>
       <c r="W95">
-        <v>0.2307679657977404</v>
+        <v>0.2308214980764879</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2134026379244931</v>
+        <v>0.2111323970955091</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2694774999150692</v>
+        <v>0.2713774999150692</v>
       </c>
       <c r="C96">
-        <v>-25.99613468358893</v>
+        <v>-26.50889141401284</v>
       </c>
       <c r="D96">
-        <v>8.412465316411074</v>
+        <v>8.341608585987162</v>
       </c>
       <c r="E96">
-        <v>38.7486</v>
+        <v>39.1905</v>
       </c>
       <c r="F96">
-        <v>41.5386</v>
+        <v>41.9805</v>
       </c>
       <c r="G96">
         <v>7.13</v>
@@ -9159,37 +9159,37 @@
         <v>2.068</v>
       </c>
       <c r="M96">
-        <v>9.794801880000001</v>
+        <v>9.8990019</v>
       </c>
       <c r="N96">
-        <v>-7.726801880000002</v>
+        <v>-7.8310019</v>
       </c>
       <c r="O96">
-        <v>-0.7726801880000003</v>
+        <v>-0.7831001900000001</v>
       </c>
       <c r="P96">
-        <v>-6.954121692000001</v>
+        <v>-7.047901710000001</v>
       </c>
       <c r="Q96">
-        <v>-6.952121692000001</v>
+        <v>-7.045901710000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8750881953861765</v>
+        <v>1.040945834463412</v>
       </c>
       <c r="T96">
-        <v>16.62197061145332</v>
+        <v>19.94636473374399</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02111323970955092</v>
+        <v>0.02089099508102933</v>
       </c>
       <c r="W96">
-        <v>0.2308214980764879</v>
+        <v>0.2308739033598933</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2111323970955091</v>
+        <v>0.2089099508102933</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2713774999150692</v>
+        <v>0.2732774999150692</v>
       </c>
       <c r="C97">
-        <v>-26.50889141401284</v>
+        <v>-27.02046448637953</v>
       </c>
       <c r="D97">
-        <v>8.341608585987162</v>
+        <v>8.271935513620477</v>
       </c>
       <c r="E97">
-        <v>39.1905</v>
+        <v>39.6324</v>
       </c>
       <c r="F97">
-        <v>41.9805</v>
+        <v>42.4224</v>
       </c>
       <c r="G97">
         <v>7.13</v>
@@ -9241,37 +9241,37 @@
         <v>2.068</v>
       </c>
       <c r="M97">
-        <v>9.8990019</v>
+        <v>10.00320192</v>
       </c>
       <c r="N97">
-        <v>-7.8310019</v>
+        <v>-7.935201920000001</v>
       </c>
       <c r="O97">
-        <v>-0.7831001900000001</v>
+        <v>-0.7935201920000001</v>
       </c>
       <c r="P97">
-        <v>-7.047901710000001</v>
+        <v>-7.141681728000001</v>
       </c>
       <c r="Q97">
-        <v>-7.045901710000001</v>
+        <v>-7.139681728000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.040945834463412</v>
+        <v>1.289732293079266</v>
       </c>
       <c r="T97">
-        <v>19.94636473374399</v>
+        <v>24.93295591718</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02089099508102933</v>
+        <v>0.02067338054893528</v>
       </c>
       <c r="W97">
-        <v>0.2308739033598933</v>
+        <v>0.2309252168665611</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2089099508102933</v>
+        <v>0.2067338054893527</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2732774999150692</v>
+        <v>0.2751774999150692</v>
       </c>
       <c r="C98">
-        <v>-27.02046448637952</v>
+        <v>-27.53088331443239</v>
       </c>
       <c r="D98">
-        <v>8.271935513620477</v>
+        <v>8.203416685567605</v>
       </c>
       <c r="E98">
-        <v>39.6324</v>
+        <v>40.0743</v>
       </c>
       <c r="F98">
-        <v>42.4224</v>
+        <v>42.8643</v>
       </c>
       <c r="G98">
         <v>7.13</v>
@@ -9323,37 +9323,37 @@
         <v>2.068</v>
       </c>
       <c r="M98">
-        <v>10.00320192</v>
+        <v>10.10740194</v>
       </c>
       <c r="N98">
-        <v>-7.935201919999999</v>
+        <v>-8.039401940000001</v>
       </c>
       <c r="O98">
-        <v>-0.7935201919999999</v>
+        <v>-0.8039401940000002</v>
       </c>
       <c r="P98">
-        <v>-7.141681727999999</v>
+        <v>-7.235461746000001</v>
       </c>
       <c r="Q98">
-        <v>-7.139681727999999</v>
+        <v>-7.233461746000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.289732293079263</v>
+        <v>1.704376390772351</v>
       </c>
       <c r="T98">
-        <v>24.93295591717994</v>
+        <v>33.24394122290659</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02067338054893528</v>
+        <v>0.02046025291441017</v>
       </c>
       <c r="W98">
-        <v>0.2309252168665611</v>
+        <v>0.2309754723627821</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2067338054893527</v>
+        <v>0.2046025291441016</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2751774999150692</v>
+        <v>0.2770774999150691</v>
       </c>
       <c r="C99">
-        <v>-27.53088331443239</v>
+        <v>-28.0401763453511</v>
       </c>
       <c r="D99">
-        <v>8.203416685567605</v>
+        <v>8.136023654648897</v>
       </c>
       <c r="E99">
-        <v>40.0743</v>
+        <v>40.5162</v>
       </c>
       <c r="F99">
-        <v>42.8643</v>
+        <v>43.3062</v>
       </c>
       <c r="G99">
         <v>7.13</v>
@@ -9405,37 +9405,37 @@
         <v>2.068</v>
       </c>
       <c r="M99">
-        <v>10.10740194</v>
+        <v>10.21160196</v>
       </c>
       <c r="N99">
-        <v>-8.039401940000001</v>
+        <v>-8.14360196</v>
       </c>
       <c r="O99">
-        <v>-0.8039401940000002</v>
+        <v>-0.814360196</v>
       </c>
       <c r="P99">
-        <v>-7.235461746000001</v>
+        <v>-7.329241764</v>
       </c>
       <c r="Q99">
-        <v>-7.233461746000001</v>
+        <v>-7.327241764</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.704376390772351</v>
+        <v>2.533664586158525</v>
       </c>
       <c r="T99">
-        <v>33.24394122290659</v>
+        <v>49.86591183435987</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02046025291441017</v>
+        <v>0.0202514748234468</v>
       </c>
       <c r="W99">
-        <v>0.2309754723627821</v>
+        <v>0.2310247022366312</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2046025291441016</v>
+        <v>0.202514748234468</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2770774999150691</v>
+        <v>0.2789774999150692</v>
       </c>
       <c r="C100">
-        <v>-28.0401763453511</v>
+        <v>-28.5483710991308</v>
       </c>
       <c r="D100">
-        <v>8.136023654648897</v>
+        <v>8.069728900869205</v>
       </c>
       <c r="E100">
-        <v>40.5162</v>
+        <v>40.9581</v>
       </c>
       <c r="F100">
-        <v>43.3062</v>
+        <v>43.7481</v>
       </c>
       <c r="G100">
         <v>7.13</v>
@@ -9487,37 +9487,37 @@
         <v>2.068</v>
       </c>
       <c r="M100">
-        <v>10.21160196</v>
+        <v>10.31580198</v>
       </c>
       <c r="N100">
-        <v>-8.14360196</v>
+        <v>-8.24780198</v>
       </c>
       <c r="O100">
-        <v>-0.814360196</v>
+        <v>-0.824780198</v>
       </c>
       <c r="P100">
-        <v>-7.329241764</v>
+        <v>-7.423021782</v>
       </c>
       <c r="Q100">
-        <v>-7.327241764</v>
+        <v>-7.421021782</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.533664586158525</v>
+        <v>5.021529172317051</v>
       </c>
       <c r="T100">
-        <v>49.86591183435987</v>
+        <v>99.73182366871974</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0202514748234468</v>
+        <v>0.02004691447169481</v>
       </c>
       <c r="W100">
-        <v>0.2310247022366312</v>
+        <v>0.2310729375675744</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.202514748234468</v>
+        <v>0.2004691447169481</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2789774999150692</v>
-      </c>
-      <c r="C101">
-        <v>-28.5483710991308</v>
-      </c>
-      <c r="D101">
-        <v>8.069728900869205</v>
-      </c>
-      <c r="E101">
-        <v>40.9581</v>
-      </c>
-      <c r="F101">
-        <v>43.7481</v>
-      </c>
-      <c r="G101">
-        <v>7.13</v>
-      </c>
-      <c r="H101">
-        <v>41.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.07</v>
-      </c>
-      <c r="K101">
-        <v>0.002</v>
-      </c>
-      <c r="L101">
-        <v>2.068</v>
-      </c>
-      <c r="M101">
-        <v>10.31580198</v>
-      </c>
-      <c r="N101">
-        <v>-8.24780198</v>
-      </c>
-      <c r="O101">
-        <v>-0.824780198</v>
-      </c>
-      <c r="P101">
-        <v>-7.423021782</v>
-      </c>
-      <c r="Q101">
-        <v>-7.421021782</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.021529172317051</v>
-      </c>
-      <c r="T101">
-        <v>99.73182366871974</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02004691447169481</v>
-      </c>
-      <c r="W101">
-        <v>0.2310729375675744</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2004691447169481</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
